--- a/Formularios de Control Ejecución Presupuestos_Proyectos.xlsx
+++ b/Formularios de Control Ejecución Presupuestos_Proyectos.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\william.boconzaca\Downloads\I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCF0315-35BD-4413-A9B0-53FE0E03F106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4419C35A-47C7-4C6F-8616-4BFD1FD2A352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-945" windowWidth="21840" windowHeight="13140" tabRatio="657" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-945" windowWidth="21840" windowHeight="13140" tabRatio="657" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Listas" sheetId="50" r:id="rId1"/>
+    <sheet name="Listas" sheetId="50" state="hidden" r:id="rId1"/>
     <sheet name="Recursos aprobados" sheetId="52" state="hidden" r:id="rId2"/>
     <sheet name="FORM RESUMEN " sheetId="44" r:id="rId3"/>
     <sheet name="FORM 1 GASTO AO&amp;M-C SPEE" sheetId="43" r:id="rId4"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="360">
   <si>
     <t>Calidad</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Otros gastos</t>
-  </si>
-  <si>
-    <t>Certificados Ambientales</t>
   </si>
   <si>
     <t>descripcion_partida</t>
@@ -1088,13 +1085,7 @@
     <t>sora</t>
   </si>
   <si>
-    <t xml:space="preserve">EE Ambato </t>
-  </si>
-  <si>
     <t>CNEL EP Eficiencia Energética</t>
-  </si>
-  <si>
-    <t>Sí</t>
   </si>
   <si>
     <t>SIGDE</t>
@@ -1158,9 +1149,6 @@
     <t>fuente</t>
   </si>
   <si>
-    <t xml:space="preserve">Aportes de accionistas </t>
-  </si>
-  <si>
     <t>servicios</t>
   </si>
   <si>
@@ -1206,9 +1194,6 @@
     <t>tipo_permiso_ambiental</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>total_gasto_AOM</t>
   </si>
   <si>
@@ -1225,6 +1210,15 @@
   </si>
   <si>
     <t>Gastos financieros</t>
+  </si>
+  <si>
+    <t>FERUM</t>
+  </si>
+  <si>
+    <t>PMD Fiscales</t>
+  </si>
+  <si>
+    <t>Aportes de accionistas</t>
   </si>
 </sst>
 </file>
@@ -2936,6 +2930,30 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="11" fillId="6" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2954,15 +2972,6 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2970,27 +2979,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3003,6 +2991,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="2" borderId="6" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -11919,9 +11913,7 @@
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="estado_proyecto" dataDxfId="262"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="etapa_ejecucion_proyecto" dataDxfId="261"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="avance_ejecucion_fisica" dataDxfId="260" dataCellStyle="Porcentaje"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="avance_ejecucion_total" dataDxfId="259">
-      <calculatedColumnFormula>+IF($Q2="No iniciado 0%",0%,IF($Q2="Elaboración de pliegos 5%",5%,IF($Q2="Disponibilidad de pliegos 10%",10%,IF($Q2="Publicación del proceso 15%",15%,IF($Q2="Resolución de adjudicación 30%",30%,IF($Q2="Adjudicación y firma de contrato 40%",40%,IF($Q2="En ejecución 41% - 90%",(40%+($R2*50%)),IF($Q2="Acta de entrega - recepción 95%",IF($R2=100%,95%,""),IF($Q2="Registro contable 100%",IF($R2=100%,100%,""),"")))))))))</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="avance_ejecucion_total" dataDxfId="259"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="fecha_inicio_proyecto" dataDxfId="258"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="fecha_pro_fin_proyecto" dataDxfId="257"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="fecha_fin_proyecto" dataDxfId="256"/>
@@ -11994,9 +11986,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="estado_proyecto" dataDxfId="193"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="etapa_ejecucion_proyecto" dataDxfId="192"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="avance_ejecucion_fisica" dataDxfId="191" dataCellStyle="Porcentaje"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="avance_ejecucion_total" dataDxfId="190">
-      <calculatedColumnFormula>+IF($M2="No iniciado 0%",0%,IF($M2="Elaboración de pliegos 5%",5%,IF($M2="Disponibilidad de pliegos 10%",10%,IF($M2="Publicación del proceso 15%",15%,IF($M2="Resolución de adjudicación 30%",30%,IF($M2="Adjudicación y firma de contrato 40%",40%,IF($M2="En ejecución 41% - 90%",(40%+($N2*50%)),IF($M2="Acta de entrega - recepción 95%",IF($N2=100%,95%,""),IF($M2="Registro contable 100%",IF($N2=100%,100%,""),"")))))))))</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="avance_ejecucion_total" dataDxfId="190"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="fecha_inicio_proyecto" dataDxfId="189"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="fecha_pro_fin_proyecto" dataDxfId="188"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="fecha_fin_proyecto" dataDxfId="187"/>
@@ -12150,9 +12140,7 @@
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="estado_proyecto" dataDxfId="64"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="etapa_ejecucion_proyecto" dataDxfId="63"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="avance_ejecucion_fisica" dataDxfId="62" dataCellStyle="Porcentaje 2"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="avance_ejecucion_total" dataDxfId="61">
-      <calculatedColumnFormula>+IF($K2="No iniciado 0%",0%,IF($K2="Elaboración de pliegos 5%",5%,IF($K2="Disponibilidad de pliegos 10%",10%,IF($K2="Publicación del proceso 15%",15%,IF($K2="Resolución de adjudicación 30%",30%,IF($K2="Adjudicación y firma de contrato 40%",40%,IF($K2="En ejecución 41% - 90%",(40%+($L2*50%)),IF($K2="Acta de entrega - recepción 95%",IF($L2=100%,95%,""),IF($K2="Registro contable 100%",IF($L2=100%,100%,""),"")))))))))</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="avance_ejecucion_total" dataDxfId="61"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0500-000010000000}" name="fecha_inicio_proyecto" dataDxfId="60" dataCellStyle="Millares 3"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0500-000011000000}" name="fecha_pro_fin_proyecto" dataDxfId="59" dataCellStyle="Millares 3"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="fecha_fin_proyecto" dataDxfId="58"/>
@@ -12202,9 +12190,7 @@
     <tableColumn id="12" xr3:uid="{D7145B13-BBAF-4645-9E9B-4FAB719B5F2C}" name="estado_proyecto" dataDxfId="18"/>
     <tableColumn id="13" xr3:uid="{7B6351B2-F92E-43A3-AD3E-A29159CDA4AD}" name="etapa_ejecucion_proyecto" dataDxfId="17"/>
     <tableColumn id="14" xr3:uid="{58CA3E44-F725-486B-8315-8BCA3F43DA55}" name="avance_ejecucion_fisica" dataDxfId="16" dataCellStyle="Porcentaje 2"/>
-    <tableColumn id="15" xr3:uid="{4C42F86A-1994-41C2-9EA9-AD9345A0B24B}" name="avance_ejecucion_total" dataDxfId="15">
-      <calculatedColumnFormula>+IF($L2="No iniciado 0%",0%,IF($L2="Elaboración de pliegos 5%",5%,IF($L2="Disponibilidad de pliegos 10%",10%,IF($L2="Publicación del proceso 15%",15%,IF($L2="Resolución de adjudicación 30%",30%,IF($L2="Adjudicación y firma de contrato 40%",40%,IF($L2="En ejecución 41% - 90%",(40%+($M2*50%)),IF($L2="Acta de entrega - recepción 95%",IF($M2=100%,95%,""),IF($L2="Registro contable 100%",IF($M2=100%,100%,""),"")))))))))</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="15" xr3:uid="{4C42F86A-1994-41C2-9EA9-AD9345A0B24B}" name="avance_ejecucion_total" dataDxfId="15"/>
     <tableColumn id="16" xr3:uid="{D17192EF-2441-48DD-BCBF-E356D434F366}" name="fecha_inicio_proyecto" dataDxfId="14" dataCellStyle="Millares 3"/>
     <tableColumn id="17" xr3:uid="{85D8B59D-8053-4403-8BB2-4D608A8ABD8A}" name="fecha_pro_fin_proyecto" dataDxfId="13" dataCellStyle="Millares 3"/>
     <tableColumn id="18" xr3:uid="{60CC09A3-5031-454C-B5EE-FDD8DD70B39A}" name="fecha_fin_proyecto" dataDxfId="12"/>
@@ -12619,55 +12605,55 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="200" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C1" s="200" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D1" s="200"/>
       <c r="E1" s="200" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G1" s="201" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I1" s="201" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K1" s="200" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="200" t="s">
-        <v>29</v>
-      </c>
       <c r="O1" s="200" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q1" s="201" t="s">
+        <v>336</v>
+      </c>
+      <c r="S1" s="201" t="s">
         <v>338</v>
       </c>
-      <c r="Q1" s="201" t="s">
-        <v>340</v>
-      </c>
-      <c r="S1" s="201" t="s">
-        <v>342</v>
-      </c>
       <c r="T1" s="216" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -12679,28 +12665,28 @@
         <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q2" s="206" t="s">
         <v>2</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="T2" s="214">
         <v>46198</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>11</v>
@@ -12709,45 +12695,45 @@
         <v>21</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q3" s="206" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T3" s="214">
         <v>46218</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>10</v>
@@ -12756,42 +12742,42 @@
         <v>14</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="206" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T4" s="214">
         <v>46251</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>7</v>
@@ -12800,30 +12786,30 @@
         <v>15</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T5" s="214">
         <v>46280</v>
@@ -12843,22 +12829,22 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="T6" s="214">
         <v>46310</v>
@@ -12869,16 +12855,16 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T7" s="214">
         <v>46342</v>
@@ -12889,16 +12875,16 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="T8" s="214">
         <v>46371</v>
@@ -12909,13 +12895,13 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="T9" s="214">
         <v>46402</v>
@@ -12926,13 +12912,13 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>226</v>
+        <v>357</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="T10" s="215">
         <v>46461</v>
@@ -12943,116 +12929,116 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="O24" s="1" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="O25" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.25">
@@ -13123,136 +13109,136 @@
   <sheetData>
     <row r="1" spans="1:44" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="190" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="190" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="190" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="190" t="s">
+      <c r="D1" s="190" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="F1" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="190" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="190" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="190" t="s">
+      <c r="H1" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="190" t="s">
-        <v>296</v>
-      </c>
-      <c r="G1" s="190" t="s">
+      <c r="I1" s="190" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="191" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="191" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="191" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="190" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="190" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="190" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="191" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="191" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="191" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="190" t="s">
+      <c r="O1" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="O1" s="190" t="s">
+      <c r="P1" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="167" t="s">
+      <c r="Q1" s="190" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="190" t="s">
+      <c r="R1" s="190" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="190" t="s">
+      <c r="S1" s="190" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="190" t="s">
+      <c r="T1" s="190" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="190" t="s">
+      <c r="U1" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="V1" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="190" t="s">
-        <v>86</v>
-      </c>
-      <c r="V1" s="190" t="s">
-        <v>49</v>
-      </c>
       <c r="W1" s="190" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X1" s="190" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="190" t="s">
+      <c r="Z1" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA1" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA1" s="190" t="s">
+      <c r="AB1" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="190" t="s">
+      <c r="AC1" s="190" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="190" t="s">
-        <v>34</v>
-      </c>
       <c r="AD1" s="190" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AE1" s="190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="190" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG1" s="190" t="s">
         <v>277</v>
       </c>
-      <c r="AG1" s="190" t="s">
+      <c r="AH1" s="190" t="s">
         <v>278</v>
       </c>
-      <c r="AH1" s="190" t="s">
+      <c r="AI1" s="190" t="s">
         <v>279</v>
       </c>
-      <c r="AI1" s="190" t="s">
+      <c r="AJ1" s="190" t="s">
         <v>280</v>
       </c>
-      <c r="AJ1" s="190" t="s">
+      <c r="AK1" s="190" t="s">
         <v>281</v>
       </c>
-      <c r="AK1" s="190" t="s">
+      <c r="AL1" s="190" t="s">
         <v>282</v>
       </c>
-      <c r="AL1" s="190" t="s">
+      <c r="AM1" s="190" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN1" s="190" t="s">
         <v>283</v>
       </c>
-      <c r="AM1" s="190" t="s">
+      <c r="AO1" s="190" t="s">
         <v>285</v>
       </c>
-      <c r="AN1" s="190" t="s">
-        <v>284</v>
-      </c>
-      <c r="AO1" s="190" t="s">
-        <v>286</v>
-      </c>
       <c r="AP1" s="190" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ1" s="190" t="s">
+        <v>302</v>
+      </c>
+      <c r="AR1" s="190" t="s">
         <v>81</v>
-      </c>
-      <c r="AQ1" s="190" t="s">
-        <v>303</v>
-      </c>
-      <c r="AR1" s="190" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
@@ -13370,124 +13356,124 @@
   <sheetData>
     <row r="1" spans="1:41" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="190" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="190" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D1" s="190" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="190" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="190" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="191" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="191" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="191" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="190" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="190" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="190" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="191" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="191" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="191" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="190" t="s">
+      <c r="L1" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="L1" s="190" t="s">
+      <c r="M1" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="167" t="s">
+      <c r="N1" s="190" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="190" t="s">
+      <c r="O1" s="190" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="190" t="s">
+      <c r="P1" s="190" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="190" t="s">
-        <v>47</v>
-      </c>
       <c r="Q1" s="190" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R1" s="190" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S1" s="190" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="T1" s="190" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="190" t="s">
+      <c r="V1" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="V1" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" s="190" t="s">
+      <c r="X1" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="190" t="s">
+      <c r="Y1" s="190" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="190" t="s">
-        <v>34</v>
-      </c>
       <c r="Z1" s="190" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA1" s="190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB1" s="190" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC1" s="190" t="s">
         <v>277</v>
       </c>
-      <c r="AC1" s="190" t="s">
+      <c r="AD1" s="190" t="s">
         <v>278</v>
       </c>
-      <c r="AD1" s="190" t="s">
+      <c r="AE1" s="190" t="s">
         <v>279</v>
       </c>
-      <c r="AE1" s="190" t="s">
+      <c r="AF1" s="190" t="s">
         <v>280</v>
       </c>
-      <c r="AF1" s="190" t="s">
+      <c r="AG1" s="190" t="s">
         <v>281</v>
       </c>
-      <c r="AG1" s="190" t="s">
+      <c r="AH1" s="190" t="s">
         <v>282</v>
       </c>
-      <c r="AH1" s="190" t="s">
+      <c r="AI1" s="190" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ1" s="190" t="s">
         <v>283</v>
       </c>
-      <c r="AI1" s="190" t="s">
+      <c r="AK1" s="190" t="s">
         <v>285</v>
       </c>
-      <c r="AJ1" s="190" t="s">
-        <v>284</v>
-      </c>
-      <c r="AK1" s="190" t="s">
-        <v>286</v>
-      </c>
       <c r="AL1" s="190" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM1" s="190" t="s">
+        <v>302</v>
+      </c>
+      <c r="AN1" s="190" t="s">
         <v>81</v>
-      </c>
-      <c r="AM1" s="190" t="s">
-        <v>303</v>
-      </c>
-      <c r="AN1" s="190" t="s">
-        <v>82</v>
       </c>
       <c r="AO1" s="197"/>
     </row>
@@ -13501,55 +13487,24 @@
       <c r="G2" s="149"/>
       <c r="H2" s="149"/>
       <c r="I2" s="149"/>
-      <c r="J2" s="169" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="149" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="198">
-        <v>0</v>
-      </c>
-      <c r="M2" s="152">
-        <f>+IF($K2="No iniciado 0%",0%,IF($K2="Elaboración de pliegos 5%",5%,IF($K2="Disponibilidad de pliegos 10%",10%,IF($K2="Publicación del proceso 15%",15%,IF($K2="Resolución de adjudicación 30%",30%,IF($K2="Adjudicación y firma de contrato 40%",40%,IF($K2="En ejecución 41% - 90%",(40%+($L2*50%)),IF($K2="Acta de entrega - recepción 95%",IF($L2=100%,95%,""),IF($K2="Registro contable 100%",IF($L2=100%,100%,""),"")))))))))</f>
-        <v>0</v>
-      </c>
+      <c r="J2" s="169"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="152"/>
       <c r="N2" s="188"/>
       <c r="O2" s="188"/>
       <c r="P2" s="149"/>
-      <c r="Q2" s="247">
-        <v>0</v>
-      </c>
-      <c r="R2" s="247">
-        <v>0</v>
-      </c>
-      <c r="S2" s="247">
-        <v>0</v>
-      </c>
-      <c r="T2" s="247">
-        <v>0</v>
-      </c>
-      <c r="U2" s="247">
-        <v>0</v>
-      </c>
-      <c r="V2" s="247">
-        <v>0</v>
-      </c>
-      <c r="W2" s="247">
-        <v>0</v>
-      </c>
-      <c r="X2" s="247">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="247">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="247">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="247">
-        <v>0</v>
-      </c>
+      <c r="Q2" s="247"/>
+      <c r="R2" s="247"/>
+      <c r="S2" s="247"/>
+      <c r="T2" s="247"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="247"/>
+      <c r="W2" s="247"/>
+      <c r="X2" s="247"/>
+      <c r="Y2" s="247"/>
+      <c r="Z2" s="247"/>
+      <c r="AA2" s="247"/>
       <c r="AB2" s="175"/>
       <c r="AC2" s="175"/>
       <c r="AD2" s="175"/>
@@ -13622,160 +13577,123 @@
   <sheetData>
     <row r="1" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="190" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="190" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C1" s="190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="190" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E1" s="190" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="190" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="190" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="191" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="191" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="191" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="190" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="190" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="190" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="191" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="191" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="191" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="190" t="s">
+      <c r="M1" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="190" t="s">
+      <c r="N1" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="167" t="s">
+      <c r="O1" s="190" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="190" t="s">
+      <c r="P1" s="190" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="190" t="s">
+      <c r="Q1" s="190" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="190" t="s">
-        <v>47</v>
-      </c>
       <c r="R1" s="190" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S1" s="190" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T1" s="190" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U1" s="190" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="190" t="s">
+      <c r="W1" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="X1" s="190" t="s">
+      <c r="Y1" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="190" t="s">
+      <c r="Z1" s="190" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="190" t="s">
-        <v>34</v>
-      </c>
       <c r="AA1" s="190" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AB1" s="190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC1" s="190" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD1" s="197"/>
     </row>
     <row r="2" spans="1:30" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="241" t="s">
-        <v>317</v>
-      </c>
-      <c r="B2" s="241" t="s">
-        <v>242</v>
-      </c>
-      <c r="C2" s="148" t="s">
-        <v>318</v>
-      </c>
-      <c r="D2" s="169" t="s">
-        <v>2</v>
-      </c>
+      <c r="A2" s="241"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="169"/>
       <c r="E2" s="170"/>
       <c r="F2" s="171"/>
       <c r="G2" s="149"/>
       <c r="H2" s="149"/>
       <c r="I2" s="149"/>
       <c r="J2" s="149"/>
-      <c r="K2" s="169" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="149" t="s">
-        <v>21</v>
-      </c>
+      <c r="K2" s="169"/>
+      <c r="L2" s="149"/>
       <c r="M2" s="198"/>
-      <c r="N2" s="152">
-        <f>+IF($L2="No iniciado 0%",0%,IF($L2="Elaboración de pliegos 5%",5%,IF($L2="Disponibilidad de pliegos 10%",10%,IF($L2="Publicación del proceso 15%",15%,IF($L2="Resolución de adjudicación 30%",30%,IF($L2="Adjudicación y firma de contrato 40%",40%,IF($L2="En ejecución 41% - 90%",(40%+($M2*50%)),IF($L2="Acta de entrega - recepción 95%",IF($M2=100%,95%,""),IF($L2="Registro contable 100%",IF($M2=100%,100%,""),"")))))))))</f>
-        <v>0</v>
-      </c>
+      <c r="N2" s="152"/>
       <c r="O2" s="188"/>
       <c r="P2" s="188"/>
       <c r="Q2" s="149"/>
-      <c r="R2" s="248">
-        <v>0</v>
-      </c>
-      <c r="S2" s="248">
-        <v>0</v>
-      </c>
-      <c r="T2" s="248">
-        <v>0</v>
-      </c>
-      <c r="U2" s="248">
-        <v>0</v>
-      </c>
-      <c r="V2" s="248">
-        <v>0</v>
-      </c>
-      <c r="W2" s="248">
-        <v>0</v>
-      </c>
-      <c r="X2" s="248">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="248">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="248">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="248">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="248">
-        <v>0</v>
-      </c>
+      <c r="R2" s="248"/>
+      <c r="S2" s="248"/>
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
+      <c r="AA2" s="248"/>
+      <c r="AB2" s="248"/>
       <c r="AC2" s="176"/>
       <c r="AD2" s="199"/>
     </row>
@@ -14520,34 +14438,34 @@
   <sheetData>
     <row r="1" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="79" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>161</v>
-      </c>
       <c r="E1" s="79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F1" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="79" t="s">
-        <v>122</v>
-      </c>
       <c r="H1" s="79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I1" s="91"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" s="108"/>
       <c r="C2" s="108"/>
@@ -14560,7 +14478,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="111" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B3" s="112">
         <f>+B4+B12+B14</f>
@@ -14594,7 +14512,7 @@
     </row>
     <row r="4" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="97" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="96">
         <f>+B5+B10+B11</f>
@@ -14628,7 +14546,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="110">
         <f>+B6+B7+B8+B9</f>
@@ -14662,7 +14580,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="98" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="99"/>
       <c r="C6" s="99"/>
@@ -14675,7 +14593,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="98" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="99"/>
       <c r="C7" s="99"/>
@@ -14688,7 +14606,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="98" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="99"/>
       <c r="C8" s="99"/>
@@ -14701,7 +14619,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="98" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="99"/>
       <c r="C9" s="99"/>
@@ -14714,7 +14632,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="109" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="110"/>
       <c r="C10" s="110"/>
@@ -14727,7 +14645,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="109" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="110"/>
       <c r="C11" s="110"/>
@@ -14740,7 +14658,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="97" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12" s="96">
         <f>+B13</f>
@@ -14774,7 +14692,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="101" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B13" s="99"/>
       <c r="C13" s="99"/>
@@ -14787,7 +14705,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="97" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B14" s="96">
         <f>+SUM(B15:B16)</f>
@@ -14821,7 +14739,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="101" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" s="99"/>
       <c r="C15" s="99"/>
@@ -14834,7 +14752,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="101" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" s="99"/>
       <c r="C16" s="99"/>
@@ -14847,7 +14765,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="204" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" s="113"/>
       <c r="C17" s="113"/>
@@ -14860,7 +14778,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="114" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B18" s="113"/>
       <c r="C18" s="113"/>
@@ -14873,7 +14791,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="204" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B19" s="113"/>
       <c r="C19" s="113"/>
@@ -14886,7 +14804,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B20" s="108">
         <f>+B21</f>
@@ -14920,7 +14838,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="101" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B21" s="99"/>
       <c r="C21" s="99"/>
@@ -14933,7 +14851,7 @@
     </row>
     <row r="22" spans="1:9" s="95" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="92" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B22" s="93">
         <f t="shared" ref="B22:H22" si="6">+B3+B17+B19+B18+B20</f>
@@ -14978,7 +14896,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B24" s="105"/>
       <c r="C24" s="105"/>
@@ -15712,33 +15630,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="95" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="79" t="s">
-        <v>180</v>
-      </c>
       <c r="C1" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="E1" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="F1" s="79" t="s">
+      <c r="G1" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="79" t="s">
-        <v>122</v>
-      </c>
       <c r="H1" s="79" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="95" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="116"/>
       <c r="C2" s="117"/>
@@ -15750,7 +15668,7 @@
     </row>
     <row r="3" spans="1:8" s="95" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" s="120"/>
       <c r="C3" s="120"/>
@@ -15762,7 +15680,7 @@
     </row>
     <row r="4" spans="1:8" s="95" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="122" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" s="123">
         <f>SUM(B3)</f>
@@ -15795,7 +15713,7 @@
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="119" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" s="124"/>
       <c r="C5" s="124"/>
@@ -15807,7 +15725,7 @@
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="125" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -15819,7 +15737,7 @@
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="124"/>
       <c r="C7" s="124"/>
@@ -15831,7 +15749,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="123" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" s="126">
         <f t="shared" ref="B8:H8" si="1">SUM(B5:B7)</f>
@@ -15864,7 +15782,7 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B9" s="116"/>
       <c r="C9" s="117"/>
@@ -15876,7 +15794,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" s="120"/>
       <c r="C10" s="120"/>
@@ -15888,7 +15806,7 @@
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="122" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B11" s="126">
         <f>SUM(B10)</f>
@@ -15921,7 +15839,7 @@
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="119" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="124"/>
       <c r="C12" s="124"/>
@@ -15933,7 +15851,7 @@
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="110" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="124"/>
       <c r="C13" s="124"/>
@@ -15945,7 +15863,7 @@
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="110" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" s="124"/>
       <c r="C14" s="124"/>
@@ -15957,7 +15875,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="123" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" s="126">
         <f t="shared" ref="B15:H15" si="3">SUM(B12:B14)</f>
@@ -15990,7 +15908,7 @@
     </row>
     <row r="16" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="127" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" s="124"/>
       <c r="C16" s="124"/>
@@ -16002,7 +15920,7 @@
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="110" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B17" s="124"/>
       <c r="C17" s="124"/>
@@ -16014,7 +15932,7 @@
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="110" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B18" s="124"/>
       <c r="C18" s="124"/>
@@ -16036,7 +15954,7 @@
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="127" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="124"/>
       <c r="C20" s="124"/>
@@ -16048,7 +15966,7 @@
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" s="124"/>
       <c r="C21" s="124"/>
@@ -16060,7 +15978,7 @@
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B22" s="124"/>
       <c r="C22" s="124"/>
@@ -16082,7 +16000,7 @@
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="110" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B24" s="124"/>
       <c r="C24" s="124"/>
@@ -16094,7 +16012,7 @@
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="110" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B25" s="124"/>
       <c r="C25" s="124"/>
@@ -16106,7 +16024,7 @@
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="205" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B26" s="129"/>
       <c r="C26" s="129"/>
@@ -16118,7 +16036,7 @@
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="110" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B27" s="130"/>
       <c r="C27" s="130"/>
@@ -16130,7 +16048,7 @@
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B28" s="126">
         <f t="shared" ref="B28:H28" si="4">+B4+B8+B11+B15+B17+B18+B21+B22+B24+B25+B27</f>
@@ -16173,7 +16091,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="104" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B30" s="105"/>
       <c r="C30" s="105"/>
@@ -16654,10 +16572,10 @@
   <sheetData>
     <row r="1" spans="1:15" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="281" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="283" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C1" s="285">
         <v>2026</v>
@@ -16679,48 +16597,48 @@
       <c r="A2" s="282"/>
       <c r="B2" s="284"/>
       <c r="C2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="22" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="20"/>
@@ -16739,7 +16657,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="24">
         <f>+B5+B11+B25+B36+B41+B42</f>
@@ -16800,7 +16718,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="5">
         <f>SUM(B6:B9)</f>
@@ -16861,7 +16779,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="68">
         <v>0</v>
@@ -16908,7 +16826,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="68">
         <v>0</v>
@@ -16955,7 +16873,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" s="68">
         <v>0</v>
@@ -17002,7 +16920,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="68">
         <v>0</v>
@@ -17049,7 +16967,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="38" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B10" s="68"/>
       <c r="C10" s="68"/>
@@ -17068,7 +16986,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" s="5">
         <f>SUM(B12:B24)</f>
@@ -17129,7 +17047,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" s="52">
         <v>0</v>
@@ -17176,7 +17094,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B13" s="52">
         <v>0</v>
@@ -17223,7 +17141,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B14" s="52">
         <v>0</v>
@@ -17270,7 +17188,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B15" s="52">
         <v>0</v>
@@ -17317,7 +17235,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B16" s="52">
         <v>0</v>
@@ -17364,7 +17282,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B17" s="52">
         <v>0</v>
@@ -17411,7 +17329,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B18" s="52">
         <v>0</v>
@@ -17458,7 +17376,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="52">
         <v>0</v>
@@ -17505,7 +17423,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B20" s="52">
         <v>0</v>
@@ -17552,7 +17470,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B21" s="52">
         <v>0</v>
@@ -17599,7 +17517,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B22" s="52">
         <v>0</v>
@@ -17646,7 +17564,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B23" s="52">
         <v>0</v>
@@ -17693,7 +17611,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B24" s="52">
         <v>0</v>
@@ -17740,7 +17658,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" s="7">
         <f>SUM(B26:B35)</f>
@@ -17801,7 +17719,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" s="52">
         <v>0</v>
@@ -17848,7 +17766,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B27" s="52">
         <v>0</v>
@@ -17895,7 +17813,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B28" s="52">
         <v>0</v>
@@ -17942,7 +17860,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B29" s="52">
         <v>0</v>
@@ -17989,7 +17907,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B30" s="52">
         <v>0</v>
@@ -18036,7 +17954,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B31" s="52">
         <v>0</v>
@@ -18083,7 +18001,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B32" s="52">
         <v>0</v>
@@ -18130,7 +18048,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B33" s="52">
         <v>0</v>
@@ -18177,7 +18095,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B34" s="52">
         <v>0</v>
@@ -18224,7 +18142,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="202" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" s="52">
         <v>0</v>
@@ -18271,7 +18189,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="7">
         <f>SUM(B37:B40)</f>
@@ -18332,7 +18250,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="203" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B37" s="52">
         <v>0</v>
@@ -18379,7 +18297,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="203" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="52">
         <v>0</v>
@@ -18426,7 +18344,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="203" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B39" s="52"/>
       <c r="C39" s="52"/>
@@ -18445,7 +18363,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="203" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B40" s="52">
         <v>0</v>
@@ -18492,7 +18410,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B41" s="53">
         <v>0</v>
@@ -18539,7 +18457,7 @@
     </row>
     <row r="42" spans="1:15" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B42" s="55">
         <v>0</v>
@@ -18586,7 +18504,7 @@
     </row>
     <row r="43" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B43" s="26">
         <f>+B44+B50+B64+B80+B81+B82</f>
@@ -18647,7 +18565,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B44" s="11">
         <f>SUM(B45:B49)</f>
@@ -18708,7 +18626,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B45" s="52">
         <v>0</v>
@@ -18755,7 +18673,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B46" s="52">
         <v>0</v>
@@ -18802,7 +18720,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B47" s="52">
         <v>0</v>
@@ -18896,7 +18814,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B49" s="52">
         <v>0</v>
@@ -18943,7 +18861,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B50" s="11">
         <f>SUM(B51:B63)</f>
@@ -19004,7 +18922,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B51" s="58">
         <v>0</v>
@@ -19051,7 +18969,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B52" s="58">
         <v>0</v>
@@ -19098,7 +19016,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B53" s="58">
         <v>0</v>
@@ -19145,7 +19063,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B54" s="58">
         <v>0</v>
@@ -19192,7 +19110,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B55" s="58">
         <v>0</v>
@@ -19239,7 +19157,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B56" s="58">
         <v>0</v>
@@ -19286,7 +19204,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B57" s="58">
         <v>0</v>
@@ -19333,7 +19251,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B58" s="58">
         <v>0</v>
@@ -19380,7 +19298,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B59" s="58">
         <v>0</v>
@@ -19427,7 +19345,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B60" s="58">
         <v>0</v>
@@ -19474,7 +19392,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B61" s="58">
         <v>0</v>
@@ -19521,7 +19439,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" s="58">
         <v>0</v>
@@ -19568,7 +19486,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B63" s="58">
         <v>0</v>
@@ -19615,7 +19533,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B64" s="64">
         <f>SUM(B65:B74)</f>
@@ -19676,7 +19594,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B65" s="58">
         <v>0</v>
@@ -19723,7 +19641,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B66" s="58">
         <v>0</v>
@@ -19770,7 +19688,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B67" s="58">
         <v>0</v>
@@ -19817,7 +19735,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="58">
         <v>0</v>
@@ -19864,7 +19782,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="58">
         <v>0</v>
@@ -19911,7 +19829,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="58">
         <v>0</v>
@@ -19958,7 +19876,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="58">
         <v>0</v>
@@ -20005,7 +19923,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="58">
         <v>0</v>
@@ -20052,7 +19970,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B73" s="58">
         <v>0</v>
@@ -20099,7 +20017,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B74" s="58">
         <v>0</v>
@@ -20146,7 +20064,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B75" s="64">
         <f>SUM(B76:B79)</f>
@@ -20207,7 +20125,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="38" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B76" s="58">
         <v>0</v>
@@ -20254,7 +20172,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B77" s="58">
         <v>0</v>
@@ -20301,7 +20219,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B78" s="58">
         <v>0</v>
@@ -20348,7 +20266,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B79" s="60">
         <v>0</v>
@@ -20395,7 +20313,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B80" s="61">
         <v>0</v>
@@ -20442,7 +20360,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" s="64">
         <v>0</v>
@@ -20489,7 +20407,7 @@
     </row>
     <row r="82" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="62">
         <v>0</v>
@@ -20536,7 +20454,7 @@
     </row>
     <row r="83" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B83" s="36">
         <f>+B4-B43</f>
@@ -20597,7 +20515,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B84" s="44">
         <v>0</v>
@@ -20644,7 +20562,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="40" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B85" s="47">
         <v>0</v>
@@ -20691,7 +20609,7 @@
     </row>
     <row r="86" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B86" s="49">
         <v>0</v>
@@ -20742,7 +20660,7 @@
     </row>
     <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B88" s="275"/>
       <c r="C88" s="276"/>
@@ -20761,7 +20679,7 @@
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B89" s="278"/>
       <c r="C89" s="279"/>
@@ -20780,12 +20698,12 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="274" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C92" s="16"/>
     </row>
@@ -20832,30 +20750,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="228" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="228" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" s="228" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1" s="228" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="228" t="s">
         <v>346</v>
       </c>
-      <c r="C1" s="228" t="s">
-        <v>329</v>
-      </c>
-      <c r="D1" s="228" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="228" t="s">
-        <v>350</v>
-      </c>
       <c r="F1" s="228" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G1" s="228" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B2" s="218">
         <v>2026</v>
@@ -20867,10 +20785,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="213">
         <v>936346.8</v>
@@ -20878,7 +20796,7 @@
     </row>
     <row r="3" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" s="218">
         <v>2026</v>
@@ -20890,10 +20808,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F3" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="213">
         <v>1835700.35</v>
@@ -20901,7 +20819,7 @@
     </row>
     <row r="4" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" s="218">
         <v>2026</v>
@@ -20913,10 +20831,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F4" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G4" s="213">
         <v>2711906.47</v>
@@ -20924,7 +20842,7 @@
     </row>
     <row r="5" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" s="218">
         <v>2026</v>
@@ -20936,10 +20854,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F5" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G5" s="213">
         <v>5356646.26</v>
@@ -20947,7 +20865,7 @@
     </row>
     <row r="6" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" s="218">
         <v>2026</v>
@@ -20959,10 +20877,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" s="213">
         <v>7685263.5499999998</v>
@@ -20970,7 +20888,7 @@
     </row>
     <row r="7" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" s="218">
         <v>2026</v>
@@ -20982,10 +20900,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F7" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G7" s="213">
         <v>1675490.27</v>
@@ -20993,7 +20911,7 @@
     </row>
     <row r="8" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" s="218">
         <v>2026</v>
@@ -21005,10 +20923,10 @@
         <v>3</v>
       </c>
       <c r="E8" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F8" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G8" s="213">
         <v>11266552.140000001</v>
@@ -21016,7 +20934,7 @@
     </row>
     <row r="9" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="218">
         <v>2026</v>
@@ -21028,10 +20946,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F9" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="213">
         <v>2234549.73</v>
@@ -21039,7 +20957,7 @@
     </row>
     <row r="10" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" s="218">
         <v>2026</v>
@@ -21051,10 +20969,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F10" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="213">
         <v>2641097.7200000002</v>
@@ -21062,7 +20980,7 @@
     </row>
     <row r="11" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="218">
         <v>2026</v>
@@ -21074,10 +20992,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F11" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="213">
         <v>1244672.33</v>
@@ -21085,7 +21003,7 @@
     </row>
     <row r="12" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B12" s="218">
         <v>2026</v>
@@ -21097,10 +21015,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F12" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" s="213">
         <v>1037213.27</v>
@@ -21108,7 +21026,7 @@
     </row>
     <row r="13" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" s="218">
         <v>2026</v>
@@ -21120,10 +21038,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F13" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="213">
         <v>526225.80000000005</v>
@@ -21131,7 +21049,7 @@
     </row>
     <row r="14" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="218">
         <v>2026</v>
@@ -21143,10 +21061,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" s="213">
         <v>240787.63</v>
@@ -21154,7 +21072,7 @@
     </row>
     <row r="15" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="218">
         <v>2026</v>
@@ -21166,10 +21084,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="213">
         <v>1981523.62</v>
@@ -21177,7 +21095,7 @@
     </row>
     <row r="16" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="218">
         <v>2026</v>
@@ -21189,10 +21107,10 @@
         <v>3</v>
       </c>
       <c r="E16" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F16" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" s="213">
         <v>1193236.25</v>
@@ -21200,7 +21118,7 @@
     </row>
     <row r="17" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" s="218">
         <v>2026</v>
@@ -21212,10 +21130,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" s="213">
         <v>906490.07</v>
@@ -21223,7 +21141,7 @@
     </row>
     <row r="18" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="218">
         <v>2026</v>
@@ -21235,10 +21153,10 @@
         <v>3</v>
       </c>
       <c r="E18" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F18" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="213">
         <v>15413061.52</v>
@@ -21246,7 +21164,7 @@
     </row>
     <row r="19" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="218">
         <v>2026</v>
@@ -21258,10 +21176,10 @@
         <v>3</v>
       </c>
       <c r="E19" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F19" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" s="213">
         <v>624590.51</v>
@@ -21269,7 +21187,7 @@
     </row>
     <row r="20" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" s="218">
         <v>2026</v>
@@ -21281,10 +21199,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F20" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G20" s="213">
         <v>1460872.65</v>
@@ -21292,7 +21210,7 @@
     </row>
     <row r="21" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B21" s="218">
         <v>2026</v>
@@ -21304,10 +21222,10 @@
         <v>3</v>
       </c>
       <c r="E21" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F21" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="213">
         <v>1358232.33</v>
@@ -21315,7 +21233,7 @@
     </row>
     <row r="22" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B22" s="218">
         <v>2026</v>
@@ -21327,10 +21245,10 @@
         <v>3</v>
       </c>
       <c r="E22" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F22" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G22" s="213">
         <v>2500608.7000000002</v>
@@ -21338,7 +21256,7 @@
     </row>
     <row r="23" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="218">
         <v>2026</v>
@@ -21350,10 +21268,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="213">
         <v>8241023.5999999996</v>
@@ -21361,7 +21279,7 @@
     </row>
     <row r="24" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="218">
         <v>2026</v>
@@ -21373,10 +21291,10 @@
         <v>3</v>
       </c>
       <c r="E24" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="213">
         <v>5064893.3</v>
@@ -21384,7 +21302,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="218">
         <v>2026</v>
@@ -21396,10 +21314,10 @@
         <v>3</v>
       </c>
       <c r="E25" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" s="213">
         <v>15355032.82</v>
@@ -21407,7 +21325,7 @@
     </row>
     <row r="26" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="218">
         <v>2026</v>
@@ -21419,10 +21337,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="213">
         <v>8265565.46</v>
@@ -21430,7 +21348,7 @@
     </row>
     <row r="27" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="218">
         <v>2026</v>
@@ -21442,10 +21360,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="213">
         <v>2477876.9</v>
@@ -21453,7 +21371,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="218">
         <v>2026</v>
@@ -21465,10 +21383,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="213">
         <v>430927.95</v>
@@ -21476,7 +21394,7 @@
     </row>
     <row r="29" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B29" s="218">
         <v>2026</v>
@@ -21488,10 +21406,10 @@
         <v>3</v>
       </c>
       <c r="E29" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G29" s="213">
         <v>4548294.9400000004</v>
@@ -21499,7 +21417,7 @@
     </row>
     <row r="30" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" s="218">
         <v>2026</v>
@@ -21511,10 +21429,10 @@
         <v>3</v>
       </c>
       <c r="E30" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G30" s="213">
         <v>3813795.33</v>
@@ -21522,7 +21440,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="218">
         <v>2026</v>
@@ -21534,10 +21452,10 @@
         <v>3</v>
       </c>
       <c r="E31" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="213">
         <v>3214077.53</v>
@@ -21545,7 +21463,7 @@
     </row>
     <row r="32" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B32" s="218">
         <v>2026</v>
@@ -21557,10 +21475,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" s="213">
         <v>2238268.9300000002</v>
@@ -21568,7 +21486,7 @@
     </row>
     <row r="33" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B33" s="218">
         <v>2026</v>
@@ -21580,10 +21498,10 @@
         <v>3</v>
       </c>
       <c r="E33" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G33" s="213">
         <v>3072685.7</v>
@@ -21591,7 +21509,7 @@
     </row>
     <row r="34" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B34" s="218">
         <v>2026</v>
@@ -21603,10 +21521,10 @@
         <v>3</v>
       </c>
       <c r="E34" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="213">
         <v>485678.12</v>
@@ -21614,7 +21532,7 @@
     </row>
     <row r="35" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B35" s="218">
         <v>2026</v>
@@ -21626,10 +21544,10 @@
         <v>3</v>
       </c>
       <c r="E35" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F35" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G35" s="213">
         <v>6009201.71</v>
@@ -21637,7 +21555,7 @@
     </row>
     <row r="36" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B36" s="218">
         <v>2026</v>
@@ -21649,10 +21567,10 @@
         <v>3</v>
       </c>
       <c r="E36" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G36" s="213">
         <v>1184884.93</v>
@@ -21660,7 +21578,7 @@
     </row>
     <row r="37" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" s="218">
         <v>2026</v>
@@ -21672,10 +21590,10 @@
         <v>3</v>
       </c>
       <c r="E37" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F37" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G37" s="213">
         <v>3044910.18</v>
@@ -21683,7 +21601,7 @@
     </row>
     <row r="38" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" s="218">
         <v>2026</v>
@@ -21695,10 +21613,10 @@
         <v>3</v>
       </c>
       <c r="E38" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F38" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G38" s="213">
         <v>421575.55</v>
@@ -21706,7 +21624,7 @@
     </row>
     <row r="39" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" s="218">
         <v>2026</v>
@@ -21718,10 +21636,10 @@
         <v>3</v>
       </c>
       <c r="E39" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F39" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G39" s="213">
         <v>1247942.8999999999</v>
@@ -21729,7 +21647,7 @@
     </row>
     <row r="40" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="218">
         <v>2026</v>
@@ -21741,10 +21659,10 @@
         <v>3</v>
       </c>
       <c r="E40" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G40" s="213">
         <v>3448991.51</v>
@@ -21752,7 +21670,7 @@
     </row>
     <row r="41" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="218">
         <v>2026</v>
@@ -21764,10 +21682,10 @@
         <v>3</v>
       </c>
       <c r="E41" s="212" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G41" s="213">
         <v>482609.41</v>
@@ -21775,7 +21693,7 @@
     </row>
     <row r="42" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="218">
         <v>2026</v>
@@ -21787,10 +21705,10 @@
         <v>4</v>
       </c>
       <c r="E42" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F42" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G42" s="213">
         <v>3483244.8</v>
@@ -21798,7 +21716,7 @@
     </row>
     <row r="43" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B43" s="218">
         <v>2026</v>
@@ -21810,10 +21728,10 @@
         <v>4</v>
       </c>
       <c r="E43" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F43" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G43" s="213">
         <v>10458576.539999999</v>
@@ -21821,7 +21739,7 @@
     </row>
     <row r="44" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="218">
         <v>2026</v>
@@ -21833,10 +21751,10 @@
         <v>4</v>
       </c>
       <c r="E44" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F44" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G44" s="213">
         <v>4120615.66</v>
@@ -21844,7 +21762,7 @@
     </row>
     <row r="45" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="218">
         <v>2026</v>
@@ -21856,10 +21774,10 @@
         <v>4</v>
       </c>
       <c r="E45" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F45" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G45" s="213">
         <v>20567368.870000001</v>
@@ -21867,7 +21785,7 @@
     </row>
     <row r="46" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B46" s="218">
         <v>2026</v>
@@ -21879,10 +21797,10 @@
         <v>4</v>
       </c>
       <c r="E46" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F46" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G46" s="213">
         <v>6770196.29</v>
@@ -21890,7 +21808,7 @@
     </row>
     <row r="47" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B47" s="218">
         <v>2026</v>
@@ -21902,10 +21820,10 @@
         <v>4</v>
       </c>
       <c r="E47" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F47" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G47" s="213">
         <v>5694426.3099999996</v>
@@ -21913,7 +21831,7 @@
     </row>
     <row r="48" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B48" s="218">
         <v>2026</v>
@@ -21925,10 +21843,10 @@
         <v>4</v>
       </c>
       <c r="E48" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F48" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G48" s="213">
         <v>8601893.6400000006</v>
@@ -21936,7 +21854,7 @@
     </row>
     <row r="49" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B49" s="218">
         <v>2026</v>
@@ -21948,10 +21866,10 @@
         <v>4</v>
       </c>
       <c r="E49" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F49" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G49" s="213">
         <v>3152076.6</v>
@@ -21959,7 +21877,7 @@
     </row>
     <row r="50" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B50" s="218">
         <v>2026</v>
@@ -21971,10 +21889,10 @@
         <v>4</v>
       </c>
       <c r="E50" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F50" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G50" s="213">
         <v>2786192.46</v>
@@ -21982,7 +21900,7 @@
     </row>
     <row r="51" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="218">
         <v>2026</v>
@@ -21994,10 +21912,10 @@
         <v>4</v>
       </c>
       <c r="E51" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F51" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G51" s="213">
         <v>8208237.4900000002</v>
@@ -22005,7 +21923,7 @@
     </row>
     <row r="52" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B52" s="218">
         <v>2026</v>
@@ -22017,10 +21935,10 @@
         <v>4</v>
       </c>
       <c r="E52" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G52" s="213">
         <v>2454547.2000000002</v>
@@ -22028,7 +21946,7 @@
     </row>
     <row r="53" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B53" s="218">
         <v>2026</v>
@@ -22040,10 +21958,10 @@
         <v>4</v>
       </c>
       <c r="E53" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G53" s="213">
         <v>237502.11</v>
@@ -22051,7 +21969,7 @@
     </row>
     <row r="54" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B54" s="218">
         <v>2026</v>
@@ -22063,10 +21981,10 @@
         <v>4</v>
       </c>
       <c r="E54" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F54" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G54" s="213">
         <v>2372147.2200000002</v>
@@ -22074,7 +21992,7 @@
     </row>
     <row r="55" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B55" s="218">
         <v>2026</v>
@@ -22086,10 +22004,10 @@
         <v>4</v>
       </c>
       <c r="E55" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G55" s="213">
         <v>14577125.48</v>
@@ -22097,7 +22015,7 @@
     </row>
     <row r="56" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B56" s="218">
         <v>2026</v>
@@ -22109,10 +22027,10 @@
         <v>4</v>
       </c>
       <c r="E56" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F56" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G56" s="213">
         <v>1743064.55</v>
@@ -22120,7 +22038,7 @@
     </row>
     <row r="57" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B57" s="218">
         <v>2026</v>
@@ -22132,10 +22050,10 @@
         <v>4</v>
       </c>
       <c r="E57" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F57" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G57" s="213">
         <v>8264866.3300000001</v>
@@ -22143,7 +22061,7 @@
     </row>
     <row r="58" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B58" s="218">
         <v>2026</v>
@@ -22155,10 +22073,10 @@
         <v>4</v>
       </c>
       <c r="E58" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F58" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G58" s="213">
         <v>2476305.16</v>
@@ -22166,7 +22084,7 @@
     </row>
     <row r="59" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B59" s="218">
         <v>2026</v>
@@ -22178,10 +22096,10 @@
         <v>4</v>
       </c>
       <c r="E59" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F59" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G59" s="213">
         <v>7982746.3399999999</v>
@@ -22189,7 +22107,7 @@
     </row>
     <row r="60" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B60" s="218">
         <v>2026</v>
@@ -22201,10 +22119,10 @@
         <v>4</v>
       </c>
       <c r="E60" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F60" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G60" s="213">
         <v>9168649.3800000008</v>
@@ -22212,7 +22130,7 @@
     </row>
     <row r="61" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B61" s="218">
         <v>2026</v>
@@ -22224,10 +22142,10 @@
         <v>4</v>
       </c>
       <c r="E61" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F61" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G61" s="213">
         <v>36316.43</v>
@@ -22235,7 +22153,7 @@
     </row>
     <row r="62" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B62" s="218">
         <v>2026</v>
@@ -22247,10 +22165,10 @@
         <v>4</v>
       </c>
       <c r="E62" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F62" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G62" s="213">
         <v>1097018.8500000001</v>
@@ -22258,7 +22176,7 @@
     </row>
     <row r="63" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B63" s="218">
         <v>2026</v>
@@ -22270,10 +22188,10 @@
         <v>4</v>
       </c>
       <c r="E63" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F63" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G63" s="213">
         <v>2451129.25</v>
@@ -22281,7 +22199,7 @@
     </row>
     <row r="64" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B64" s="218">
         <v>2026</v>
@@ -22293,10 +22211,10 @@
         <v>4</v>
       </c>
       <c r="E64" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F64" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G64" s="213">
         <v>1387084.44</v>
@@ -22304,7 +22222,7 @@
     </row>
     <row r="65" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65" s="218">
         <v>2026</v>
@@ -22316,10 +22234,10 @@
         <v>4</v>
       </c>
       <c r="E65" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F65" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G65" s="213">
         <v>11612494.140000001</v>
@@ -22327,7 +22245,7 @@
     </row>
     <row r="66" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" s="218">
         <v>2026</v>
@@ -22339,10 +22257,10 @@
         <v>4</v>
       </c>
       <c r="E66" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F66" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G66" s="213">
         <v>8772546.3100000005</v>
@@ -22350,7 +22268,7 @@
     </row>
     <row r="67" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B67" s="218">
         <v>2026</v>
@@ -22362,10 +22280,10 @@
         <v>4</v>
       </c>
       <c r="E67" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F67" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" s="213">
         <v>2663781.56</v>
@@ -22373,7 +22291,7 @@
     </row>
     <row r="68" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" s="218">
         <v>2026</v>
@@ -22385,10 +22303,10 @@
         <v>4</v>
       </c>
       <c r="E68" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F68" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G68" s="213">
         <v>6466746.3700000001</v>
@@ -22396,7 +22314,7 @@
     </row>
     <row r="69" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B69" s="218">
         <v>2026</v>
@@ -22408,10 +22326,10 @@
         <v>4</v>
       </c>
       <c r="E69" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F69" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G69" s="213">
         <v>2305.7199999999998</v>
@@ -22419,7 +22337,7 @@
     </row>
     <row r="70" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B70" s="218">
         <v>2026</v>
@@ -22431,10 +22349,10 @@
         <v>4</v>
       </c>
       <c r="E70" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F70" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G70" s="213">
         <v>1928227.54</v>
@@ -22442,7 +22360,7 @@
     </row>
     <row r="71" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B71" s="218">
         <v>2026</v>
@@ -22454,10 +22372,10 @@
         <v>4</v>
       </c>
       <c r="E71" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F71" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G71" s="213">
         <v>3317208</v>
@@ -22465,7 +22383,7 @@
     </row>
     <row r="72" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B72" s="218">
         <v>2026</v>
@@ -22477,10 +22395,10 @@
         <v>4</v>
       </c>
       <c r="E72" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F72" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G72" s="213">
         <v>1887998.34</v>
@@ -22488,7 +22406,7 @@
     </row>
     <row r="73" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B73" s="218">
         <v>2026</v>
@@ -22500,10 +22418,10 @@
         <v>4</v>
       </c>
       <c r="E73" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F73" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G73" s="213">
         <v>1761355.97</v>
@@ -22511,7 +22429,7 @@
     </row>
     <row r="74" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" s="218">
         <v>2026</v>
@@ -22523,10 +22441,10 @@
         <v>4</v>
       </c>
       <c r="E74" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F74" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G74" s="213">
         <v>343539.34</v>
@@ -22534,7 +22452,7 @@
     </row>
     <row r="75" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75" s="218">
         <v>2026</v>
@@ -22546,10 +22464,10 @@
         <v>4</v>
       </c>
       <c r="E75" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F75" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G75" s="213">
         <v>5687986.5099999998</v>
@@ -22557,7 +22475,7 @@
     </row>
     <row r="76" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B76" s="218">
         <v>2026</v>
@@ -22569,10 +22487,10 @@
         <v>4</v>
       </c>
       <c r="E76" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F76" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G76" s="213">
         <v>1610840.4</v>
@@ -22580,7 +22498,7 @@
     </row>
     <row r="77" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B77" s="218">
         <v>2026</v>
@@ -22592,10 +22510,10 @@
         <v>4</v>
       </c>
       <c r="E77" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F77" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G77" s="213">
         <v>2081749.95</v>
@@ -22603,7 +22521,7 @@
     </row>
     <row r="78" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B78" s="218">
         <v>2026</v>
@@ -22615,10 +22533,10 @@
         <v>4</v>
       </c>
       <c r="E78" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F78" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G78" s="213">
         <v>24022654.059999999</v>
@@ -22626,7 +22544,7 @@
     </row>
     <row r="79" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B79" s="218">
         <v>2026</v>
@@ -22638,10 +22556,10 @@
         <v>4</v>
       </c>
       <c r="E79" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F79" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G79" s="213">
         <v>1695339.1</v>
@@ -22649,7 +22567,7 @@
     </row>
     <row r="80" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80" s="218">
         <v>2026</v>
@@ -22661,10 +22579,10 @@
         <v>4</v>
       </c>
       <c r="E80" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F80" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G80" s="213">
         <v>2037020.27</v>
@@ -22672,7 +22590,7 @@
     </row>
     <row r="81" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81" s="218">
         <v>2026</v>
@@ -22684,10 +22602,10 @@
         <v>4</v>
       </c>
       <c r="E81" s="212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F81" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G81" s="213">
         <v>672971.99</v>
@@ -22695,7 +22613,7 @@
     </row>
     <row r="82" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B82" s="218">
         <v>2026</v>
@@ -22707,10 +22625,10 @@
         <v>4</v>
       </c>
       <c r="E82" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F82" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G82" s="213">
         <v>2537178.2200000002</v>
@@ -22718,7 +22636,7 @@
     </row>
     <row r="83" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B83" s="218">
         <v>2026</v>
@@ -22730,10 +22648,10 @@
         <v>4</v>
       </c>
       <c r="E83" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G83" s="213">
         <v>656200.02</v>
@@ -22741,7 +22659,7 @@
     </row>
     <row r="84" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B84" s="218">
         <v>2026</v>
@@ -22753,10 +22671,10 @@
         <v>4</v>
       </c>
       <c r="E84" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F84" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G84" s="213">
         <v>2021299.84</v>
@@ -22764,7 +22682,7 @@
     </row>
     <row r="85" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B85" s="218">
         <v>2026</v>
@@ -22776,10 +22694,10 @@
         <v>4</v>
       </c>
       <c r="E85" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F85" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G85" s="213">
         <v>6733293.79</v>
@@ -22787,7 +22705,7 @@
     </row>
     <row r="86" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B86" s="218">
         <v>2026</v>
@@ -22799,10 +22717,10 @@
         <v>4</v>
       </c>
       <c r="E86" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F86" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G86" s="213">
         <v>6982272.2000000002</v>
@@ -22810,7 +22728,7 @@
     </row>
     <row r="87" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B87" s="218">
         <v>2026</v>
@@ -22822,10 +22740,10 @@
         <v>4</v>
       </c>
       <c r="E87" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F87" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G87" s="213">
         <v>903791.64</v>
@@ -22833,7 +22751,7 @@
     </row>
     <row r="88" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B88" s="218">
         <v>2026</v>
@@ -22845,10 +22763,10 @@
         <v>4</v>
       </c>
       <c r="E88" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F88" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G88" s="213">
         <v>1440927.52</v>
@@ -22856,7 +22774,7 @@
     </row>
     <row r="89" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B89" s="218">
         <v>2026</v>
@@ -22868,10 +22786,10 @@
         <v>4</v>
       </c>
       <c r="E89" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F89" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G89" s="213">
         <v>4082215.66</v>
@@ -22879,7 +22797,7 @@
     </row>
     <row r="90" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B90" s="218">
         <v>2026</v>
@@ -22891,10 +22809,10 @@
         <v>4</v>
       </c>
       <c r="E90" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F90" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G90" s="213">
         <v>2698409.16</v>
@@ -22902,7 +22820,7 @@
     </row>
     <row r="91" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B91" s="218">
         <v>2026</v>
@@ -22914,10 +22832,10 @@
         <v>4</v>
       </c>
       <c r="E91" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F91" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G91" s="213">
         <v>4250521.95</v>
@@ -22925,7 +22843,7 @@
     </row>
     <row r="92" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B92" s="218">
         <v>2026</v>
@@ -22937,10 +22855,10 @@
         <v>4</v>
       </c>
       <c r="E92" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F92" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G92" s="213">
         <v>3831633.22</v>
@@ -22948,7 +22866,7 @@
     </row>
     <row r="93" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B93" s="218">
         <v>2026</v>
@@ -22960,10 +22878,10 @@
         <v>4</v>
       </c>
       <c r="E93" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G93" s="213">
         <v>9603802.9100000001</v>
@@ -22971,7 +22889,7 @@
     </row>
     <row r="94" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" s="218">
         <v>2026</v>
@@ -22983,10 +22901,10 @@
         <v>4</v>
       </c>
       <c r="E94" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F94" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G94" s="213">
         <v>373328.34</v>
@@ -22994,7 +22912,7 @@
     </row>
     <row r="95" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B95" s="218">
         <v>2026</v>
@@ -23006,10 +22924,10 @@
         <v>4</v>
       </c>
       <c r="E95" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F95" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G95" s="213">
         <v>10758808.890000001</v>
@@ -23017,7 +22935,7 @@
     </row>
     <row r="96" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="218">
         <v>2026</v>
@@ -23029,10 +22947,10 @@
         <v>4</v>
       </c>
       <c r="E96" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F96" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G96" s="213">
         <v>4621971.18</v>
@@ -23040,7 +22958,7 @@
     </row>
     <row r="97" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="218">
         <v>2026</v>
@@ -23052,10 +22970,10 @@
         <v>4</v>
       </c>
       <c r="E97" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F97" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G97" s="213">
         <v>134889.71</v>
@@ -23063,7 +22981,7 @@
     </row>
     <row r="98" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" s="218">
         <v>2026</v>
@@ -23075,10 +22993,10 @@
         <v>4</v>
       </c>
       <c r="E98" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F98" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G98" s="213">
         <v>29525322.079999998</v>
@@ -23086,7 +23004,7 @@
     </row>
     <row r="99" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B99" s="218">
         <v>2026</v>
@@ -23098,10 +23016,10 @@
         <v>4</v>
       </c>
       <c r="E99" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F99" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G99" s="213">
         <v>89705.55</v>
@@ -23109,7 +23027,7 @@
     </row>
     <row r="100" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B100" s="218">
         <v>2026</v>
@@ -23121,10 +23039,10 @@
         <v>4</v>
       </c>
       <c r="E100" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F100" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G100" s="213">
         <v>222634.15</v>
@@ -23132,7 +23050,7 @@
     </row>
     <row r="101" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="218">
         <v>2026</v>
@@ -23144,10 +23062,10 @@
         <v>4</v>
       </c>
       <c r="E101" s="212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F101" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G101" s="213">
         <v>12068.07</v>
@@ -23155,7 +23073,7 @@
     </row>
     <row r="102" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="218">
         <v>2026</v>
@@ -23167,10 +23085,10 @@
         <v>5</v>
       </c>
       <c r="E102" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F102" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G102" s="213">
         <v>4520372.1714205891</v>
@@ -23178,7 +23096,7 @@
     </row>
     <row r="103" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B103" s="218">
         <v>2026</v>
@@ -23190,10 +23108,10 @@
         <v>5</v>
       </c>
       <c r="E103" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F103" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G103" s="213">
         <v>482877.72771898704</v>
@@ -23201,7 +23119,7 @@
     </row>
     <row r="104" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B104" s="218">
         <v>2026</v>
@@ -23213,10 +23131,10 @@
         <v>5</v>
       </c>
       <c r="E104" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F104" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G104" s="213">
         <v>5885041.8213627795</v>
@@ -23224,7 +23142,7 @@
     </row>
     <row r="105" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B105" s="218">
         <v>2026</v>
@@ -23236,10 +23154,10 @@
         <v>5</v>
       </c>
       <c r="E105" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F105" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G105" s="213">
         <v>2432425.769185184</v>
@@ -23247,7 +23165,7 @@
     </row>
     <row r="106" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B106" s="218">
         <v>2026</v>
@@ -23259,10 +23177,10 @@
         <v>5</v>
       </c>
       <c r="E106" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F106" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G106" s="213">
         <v>3282580.6816909611</v>
@@ -23270,7 +23188,7 @@
     </row>
     <row r="107" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B107" s="218">
         <v>2026</v>
@@ -23282,10 +23200,10 @@
         <v>5</v>
       </c>
       <c r="E107" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F107" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G107" s="213">
         <v>16796465.649125606</v>
@@ -23293,7 +23211,7 @@
     </row>
     <row r="108" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B108" s="218">
         <v>2026</v>
@@ -23305,10 +23223,10 @@
         <v>5</v>
       </c>
       <c r="E108" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F108" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G108" s="213">
         <v>2459015.5355057828</v>
@@ -23316,7 +23234,7 @@
     </row>
     <row r="109" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B109" s="218">
         <v>2026</v>
@@ -23328,10 +23246,10 @@
         <v>5</v>
       </c>
       <c r="E109" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F109" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G109" s="213">
         <v>3840965.8052022271</v>
@@ -23339,7 +23257,7 @@
     </row>
     <row r="110" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" s="218">
         <v>2026</v>
@@ -23351,10 +23269,10 @@
         <v>5</v>
       </c>
       <c r="E110" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F110" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G110" s="213">
         <v>205035.19061658921</v>
@@ -23362,7 +23280,7 @@
     </row>
     <row r="111" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B111" s="218">
         <v>2026</v>
@@ -23374,10 +23292,10 @@
         <v>5</v>
       </c>
       <c r="E111" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F111" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G111" s="213">
         <v>895996.79933667905</v>
@@ -23385,7 +23303,7 @@
     </row>
     <row r="112" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B112" s="218">
         <v>2026</v>
@@ -23397,10 +23315,10 @@
         <v>5</v>
       </c>
       <c r="E112" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F112" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G112" s="213">
         <v>2199820.3414014718</v>
@@ -23408,7 +23326,7 @@
     </row>
     <row r="113" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B113" s="218">
         <v>2026</v>
@@ -23420,10 +23338,10 @@
         <v>5</v>
       </c>
       <c r="E113" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F113" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G113" s="213">
         <v>2200896.2492160802</v>
@@ -23431,7 +23349,7 @@
     </row>
     <row r="114" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B114" s="218">
         <v>2026</v>
@@ -23443,10 +23361,10 @@
         <v>5</v>
       </c>
       <c r="E114" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F114" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G114" s="213">
         <v>41980166.552033141</v>
@@ -23454,7 +23372,7 @@
     </row>
     <row r="115" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B115" s="218">
         <v>2026</v>
@@ -23466,10 +23384,10 @@
         <v>5</v>
       </c>
       <c r="E115" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F115" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G115" s="213">
         <v>6960803.4790286636</v>
@@ -23477,7 +23395,7 @@
     </row>
     <row r="116" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B116" s="218">
         <v>2026</v>
@@ -23489,10 +23407,10 @@
         <v>5</v>
       </c>
       <c r="E116" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F116" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G116" s="213">
         <v>2367444.8130047042</v>
@@ -23500,7 +23418,7 @@
     </row>
     <row r="117" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B117" s="218">
         <v>2026</v>
@@ -23512,10 +23430,10 @@
         <v>5</v>
       </c>
       <c r="E117" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F117" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G117" s="213">
         <v>11186789.084472315</v>
@@ -23523,7 +23441,7 @@
     </row>
     <row r="118" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B118" s="218">
         <v>2026</v>
@@ -23535,10 +23453,10 @@
         <v>5</v>
       </c>
       <c r="E118" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F118" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G118" s="213">
         <v>8540349.7008952685</v>
@@ -23546,7 +23464,7 @@
     </row>
     <row r="119" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B119" s="218">
         <v>2026</v>
@@ -23558,10 +23476,10 @@
         <v>5</v>
       </c>
       <c r="E119" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F119" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G119" s="213">
         <v>3689605.7254248103</v>
@@ -23569,7 +23487,7 @@
     </row>
     <row r="120" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B120" s="218">
         <v>2026</v>
@@ -23581,10 +23499,10 @@
         <v>5</v>
       </c>
       <c r="E120" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F120" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G120" s="213">
         <v>7633556.6665072348</v>
@@ -23592,7 +23510,7 @@
     </row>
     <row r="121" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B121" s="218">
         <v>2026</v>
@@ -23604,10 +23522,10 @@
         <v>5</v>
       </c>
       <c r="E121" s="212" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F121" s="212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G121" s="213">
         <v>669312.4379031253</v>
@@ -23615,7 +23533,7 @@
     </row>
     <row r="122" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B122" s="218">
         <v>2026</v>
@@ -23630,7 +23548,7 @@
         <v>6</v>
       </c>
       <c r="F122" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G122" s="222">
         <v>8201381.7196719497</v>
@@ -23638,7 +23556,7 @@
     </row>
     <row r="123" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B123" s="218">
         <v>2026</v>
@@ -23653,7 +23571,7 @@
         <v>6</v>
       </c>
       <c r="F123" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G123" s="222">
         <v>1119849.962845041</v>
@@ -23661,7 +23579,7 @@
     </row>
     <row r="124" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B124" s="218">
         <v>2026</v>
@@ -23676,7 +23594,7 @@
         <v>6</v>
       </c>
       <c r="F124" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G124" s="222">
         <v>8440779.4223962445</v>
@@ -23684,7 +23602,7 @@
     </row>
     <row r="125" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B125" s="218">
         <v>2026</v>
@@ -23699,7 +23617,7 @@
         <v>6</v>
       </c>
       <c r="F125" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G125" s="222">
         <v>3480478.4589789868</v>
@@ -23707,7 +23625,7 @@
     </row>
     <row r="126" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B126" s="218">
         <v>2026</v>
@@ -23722,7 +23640,7 @@
         <v>6</v>
       </c>
       <c r="F126" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G126" s="222">
         <v>6335404.0858337395</v>
@@ -23730,7 +23648,7 @@
     </row>
     <row r="127" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B127" s="218">
         <v>2026</v>
@@ -23745,7 +23663,7 @@
         <v>6</v>
       </c>
       <c r="F127" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G127" s="222">
         <v>27851631.959023084</v>
@@ -23753,7 +23671,7 @@
     </row>
     <row r="128" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B128" s="218">
         <v>2026</v>
@@ -23768,7 +23686,7 @@
         <v>6</v>
       </c>
       <c r="F128" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G128" s="222">
         <v>2865161.5438282336</v>
@@ -23776,7 +23694,7 @@
     </row>
     <row r="129" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B129" s="218">
         <v>2026</v>
@@ -23791,7 +23709,7 @@
         <v>6</v>
       </c>
       <c r="F129" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G129" s="222">
         <v>6311109.5564868934</v>
@@ -23799,7 +23717,7 @@
     </row>
     <row r="130" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B130" s="218">
         <v>2026</v>
@@ -23814,7 +23732,7 @@
         <v>6</v>
       </c>
       <c r="F130" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G130" s="222">
         <v>1568671.3374811981</v>
@@ -23822,7 +23740,7 @@
     </row>
     <row r="131" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B131" s="218">
         <v>2026</v>
@@ -23837,7 +23755,7 @@
         <v>6</v>
       </c>
       <c r="F131" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G131" s="222">
         <v>3068191.3952261643</v>
@@ -23845,7 +23763,7 @@
     </row>
     <row r="132" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B132" s="218">
         <v>2026</v>
@@ -23860,7 +23778,7 @@
         <v>6</v>
       </c>
       <c r="F132" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G132" s="222">
         <v>14057719.790068243</v>
@@ -23868,7 +23786,7 @@
     </row>
     <row r="133" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B133" s="218">
         <v>2026</v>
@@ -23883,7 +23801,7 @@
         <v>6</v>
       </c>
       <c r="F133" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G133" s="222">
         <v>4660521.5659891702</v>
@@ -23891,7 +23809,7 @@
     </row>
     <row r="134" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B134" s="218">
         <v>2026</v>
@@ -23906,7 +23824,7 @@
         <v>6</v>
       </c>
       <c r="F134" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G134" s="222">
         <v>15062403.798605053</v>
@@ -23914,7 +23832,7 @@
     </row>
     <row r="135" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B135" s="218">
         <v>2026</v>
@@ -23929,7 +23847,7 @@
         <v>6</v>
       </c>
       <c r="F135" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G135" s="222">
         <v>24051547.611710619</v>
@@ -23937,7 +23855,7 @@
     </row>
     <row r="136" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B136" s="218">
         <v>2026</v>
@@ -23952,7 +23870,7 @@
         <v>6</v>
       </c>
       <c r="F136" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G136" s="222">
         <v>3781657.1834419123</v>
@@ -23960,7 +23878,7 @@
     </row>
     <row r="137" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B137" s="218">
         <v>2026</v>
@@ -23975,7 +23893,7 @@
         <v>6</v>
       </c>
       <c r="F137" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G137" s="222">
         <v>14366589.319524646</v>
@@ -23983,7 +23901,7 @@
     </row>
     <row r="138" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B138" s="218">
         <v>2026</v>
@@ -23998,7 +23916,7 @@
         <v>6</v>
       </c>
       <c r="F138" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G138" s="222">
         <v>4504131.9912612159</v>
@@ -24006,7 +23924,7 @@
     </row>
     <row r="139" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B139" s="218">
         <v>2026</v>
@@ -24021,7 +23939,7 @@
         <v>6</v>
       </c>
       <c r="F139" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G139" s="222">
         <v>4426169.1645109896</v>
@@ -24029,7 +23947,7 @@
     </row>
     <row r="140" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B140" s="218">
         <v>2026</v>
@@ -24044,7 +23962,7 @@
         <v>6</v>
       </c>
       <c r="F140" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G140" s="222">
         <v>9808801.9648041744</v>
@@ -24052,7 +23970,7 @@
     </row>
     <row r="141" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B141" s="218">
         <v>2026</v>
@@ -24067,7 +23985,7 @@
         <v>6</v>
       </c>
       <c r="F141" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G141" s="222">
         <v>3367893.9198426898</v>
@@ -24075,7 +23993,7 @@
     </row>
     <row r="142" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B142" s="218">
         <v>2026</v>
@@ -24084,13 +24002,13 @@
         <v>2</v>
       </c>
       <c r="D142" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E142" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F142" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G142" s="222">
         <v>1048764.6600996603</v>
@@ -24098,7 +24016,7 @@
     </row>
     <row r="143" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B143" s="218">
         <v>2026</v>
@@ -24107,13 +24025,13 @@
         <v>2</v>
       </c>
       <c r="D143" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E143" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F143" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G143" s="222">
         <v>260636.49000000002</v>
@@ -24121,7 +24039,7 @@
     </row>
     <row r="144" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B144" s="218">
         <v>2026</v>
@@ -24130,13 +24048,13 @@
         <v>2</v>
       </c>
       <c r="D144" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E144" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F144" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G144" s="222">
         <v>4702476.43</v>
@@ -24144,7 +24062,7 @@
     </row>
     <row r="145" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B145" s="218">
         <v>2026</v>
@@ -24153,13 +24071,13 @@
         <v>2</v>
       </c>
       <c r="D145" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E145" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F145" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G145" s="222">
         <v>996326.33000000019</v>
@@ -24167,7 +24085,7 @@
     </row>
     <row r="146" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B146" s="218">
         <v>2026</v>
@@ -24176,13 +24094,13 @@
         <v>2</v>
       </c>
       <c r="D146" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E146" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F146" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G146" s="222">
         <v>2702002.7799999993</v>
@@ -24190,7 +24108,7 @@
     </row>
     <row r="147" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B147" s="218">
         <v>2026</v>
@@ -24199,13 +24117,13 @@
         <v>2</v>
       </c>
       <c r="D147" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E147" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F147" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G147" s="222">
         <v>5632190.0200000005</v>
@@ -24213,7 +24131,7 @@
     </row>
     <row r="148" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B148" s="218">
         <v>2026</v>
@@ -24222,13 +24140,13 @@
         <v>2</v>
       </c>
       <c r="D148" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E148" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F148" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G148" s="222">
         <v>1467898.7399999998</v>
@@ -24236,7 +24154,7 @@
     </row>
     <row r="149" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B149" s="218">
         <v>2026</v>
@@ -24245,13 +24163,13 @@
         <v>2</v>
       </c>
       <c r="D149" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E149" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F149" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G149" s="222">
         <v>1848137.0899999999</v>
@@ -24259,7 +24177,7 @@
     </row>
     <row r="150" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B150" s="218">
         <v>2026</v>
@@ -24268,13 +24186,13 @@
         <v>2</v>
       </c>
       <c r="D150" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E150" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F150" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G150" s="222">
         <v>2963529.16</v>
@@ -24282,7 +24200,7 @@
     </row>
     <row r="151" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B151" s="218">
         <v>2026</v>
@@ -24291,13 +24209,13 @@
         <v>2</v>
       </c>
       <c r="D151" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E151" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F151" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G151" s="222">
         <v>1384119.6600000001</v>
@@ -24305,7 +24223,7 @@
     </row>
     <row r="152" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B152" s="218">
         <v>2026</v>
@@ -24314,13 +24232,13 @@
         <v>2</v>
       </c>
       <c r="D152" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E152" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F152" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G152" s="222">
         <v>2853879.3399999989</v>
@@ -24328,7 +24246,7 @@
     </row>
     <row r="153" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B153" s="218">
         <v>2026</v>
@@ -24337,13 +24255,13 @@
         <v>2</v>
       </c>
       <c r="D153" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E153" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F153" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G153" s="222">
         <v>1619606.37</v>
@@ -24351,7 +24269,7 @@
     </row>
     <row r="154" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B154" s="218">
         <v>2026</v>
@@ -24360,13 +24278,13 @@
         <v>2</v>
       </c>
       <c r="D154" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E154" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F154" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G154" s="222">
         <v>5266270.68</v>
@@ -24374,7 +24292,7 @@
     </row>
     <row r="155" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B155" s="218">
         <v>2026</v>
@@ -24383,13 +24301,13 @@
         <v>2</v>
       </c>
       <c r="D155" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E155" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F155" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G155" s="222">
         <v>3362532.01</v>
@@ -24397,7 +24315,7 @@
     </row>
     <row r="156" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B156" s="218">
         <v>2026</v>
@@ -24406,13 +24324,13 @@
         <v>2</v>
       </c>
       <c r="D156" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E156" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F156" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G156" s="222">
         <v>1403417.2499999998</v>
@@ -24420,7 +24338,7 @@
     </row>
     <row r="157" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B157" s="218">
         <v>2026</v>
@@ -24429,13 +24347,13 @@
         <v>2</v>
       </c>
       <c r="D157" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E157" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F157" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G157" s="222">
         <v>5457525.75</v>
@@ -24443,7 +24361,7 @@
     </row>
     <row r="158" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B158" s="218">
         <v>2026</v>
@@ -24452,13 +24370,13 @@
         <v>2</v>
       </c>
       <c r="D158" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E158" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F158" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G158" s="222">
         <v>1861035.5</v>
@@ -24466,7 +24384,7 @@
     </row>
     <row r="159" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B159" s="218">
         <v>2026</v>
@@ -24475,13 +24393,13 @@
         <v>2</v>
       </c>
       <c r="D159" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E159" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F159" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G159" s="222">
         <v>2690284.1499999994</v>
@@ -24489,7 +24407,7 @@
     </row>
     <row r="160" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B160" s="218">
         <v>2026</v>
@@ -24498,13 +24416,13 @@
         <v>2</v>
       </c>
       <c r="D160" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E160" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F160" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G160" s="222">
         <v>2781646.8600000003</v>
@@ -24512,7 +24430,7 @@
     </row>
     <row r="161" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B161" s="218">
         <v>2026</v>
@@ -24521,13 +24439,13 @@
         <v>2</v>
       </c>
       <c r="D161" s="218" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E161" s="221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F161" s="218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G161" s="222">
         <v>1357891.28</v>
@@ -24535,22 +24453,22 @@
     </row>
     <row r="162" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B162" s="218">
         <v>2026</v>
       </c>
       <c r="C162" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D162" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E162" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F162" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G162" s="222">
         <v>1313889</v>
@@ -24558,22 +24476,22 @@
     </row>
     <row r="163" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="220" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B163" s="218">
         <v>2026</v>
       </c>
       <c r="C163" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D163" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E163" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F163" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G163" s="222">
         <v>264985</v>
@@ -24581,22 +24499,22 @@
     </row>
     <row r="164" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B164" s="218">
         <v>2026</v>
       </c>
       <c r="C164" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D164" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E164" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F164" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G164" s="222">
         <v>3013150</v>
@@ -24604,22 +24522,22 @@
     </row>
     <row r="165" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="220" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B165" s="218">
         <v>2026</v>
       </c>
       <c r="C165" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D165" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E165" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F165" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G165" s="222">
         <v>661000</v>
@@ -24627,22 +24545,22 @@
     </row>
     <row r="166" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="220" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B166" s="218">
         <v>2026</v>
       </c>
       <c r="C166" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D166" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E166" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F166" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G166" s="222">
         <v>1366497</v>
@@ -24650,22 +24568,22 @@
     </row>
     <row r="167" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="220" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B167" s="218">
         <v>2026</v>
       </c>
       <c r="C167" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D167" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E167" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F167" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G167" s="222">
         <v>6849474</v>
@@ -24673,22 +24591,22 @@
     </row>
     <row r="168" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="220" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B168" s="218">
         <v>2026</v>
       </c>
       <c r="C168" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D168" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E168" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F168" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G168" s="222">
         <v>543587</v>
@@ -24696,22 +24614,22 @@
     </row>
     <row r="169" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B169" s="218">
         <v>2026</v>
       </c>
       <c r="C169" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D169" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E169" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F169" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G169" s="222">
         <v>1133028</v>
@@ -24719,22 +24637,22 @@
     </row>
     <row r="170" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B170" s="218">
         <v>2026</v>
       </c>
       <c r="C170" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D170" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E170" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F170" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G170" s="222">
         <v>265924</v>
@@ -24742,22 +24660,22 @@
     </row>
     <row r="171" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B171" s="218">
         <v>2026</v>
       </c>
       <c r="C171" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D171" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E171" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F171" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G171" s="222">
         <v>839348</v>
@@ -24765,22 +24683,22 @@
     </row>
     <row r="172" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B172" s="218">
         <v>2026</v>
       </c>
       <c r="C172" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D172" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E172" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F172" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G172" s="222">
         <v>1860806</v>
@@ -24788,22 +24706,22 @@
     </row>
     <row r="173" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B173" s="218">
         <v>2026</v>
       </c>
       <c r="C173" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D173" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E173" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F173" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G173" s="222">
         <v>1524261</v>
@@ -24811,22 +24729,22 @@
     </row>
     <row r="174" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B174" s="218">
         <v>2026</v>
       </c>
       <c r="C174" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D174" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E174" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F174" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G174" s="222">
         <v>6509725</v>
@@ -24834,22 +24752,22 @@
     </row>
     <row r="175" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B175" s="218">
         <v>2026</v>
       </c>
       <c r="C175" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D175" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E175" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F175" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G175" s="222">
         <v>1558941</v>
@@ -24857,22 +24775,22 @@
     </row>
     <row r="176" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B176" s="218">
         <v>2026</v>
       </c>
       <c r="C176" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D176" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E176" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F176" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G176" s="222">
         <v>502876</v>
@@ -24880,22 +24798,22 @@
     </row>
     <row r="177" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="220" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B177" s="218">
         <v>2026</v>
       </c>
       <c r="C177" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D177" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E177" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F177" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G177" s="222">
         <v>3166901</v>
@@ -24903,22 +24821,22 @@
     </row>
     <row r="178" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="220" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B178" s="218">
         <v>2026</v>
       </c>
       <c r="C178" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D178" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E178" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F178" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G178" s="222">
         <v>1759639</v>
@@ -24926,22 +24844,22 @@
     </row>
     <row r="179" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="220" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B179" s="218">
         <v>2026</v>
       </c>
       <c r="C179" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D179" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E179" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F179" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G179" s="222">
         <v>1036975</v>
@@ -24949,22 +24867,22 @@
     </row>
     <row r="180" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B180" s="218">
         <v>2026</v>
       </c>
       <c r="C180" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D180" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E180" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F180" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G180" s="222">
         <v>2937575</v>
@@ -24972,22 +24890,22 @@
     </row>
     <row r="181" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B181" s="218">
         <v>2026</v>
       </c>
       <c r="C181" s="218" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D181" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E181" s="221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F181" s="218" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G181" s="222">
         <v>832273</v>
@@ -25713,7 +25631,7 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="85"/>
       <c r="B1" s="70" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -25729,7 +25647,7 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="85"/>
       <c r="B2" s="70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
@@ -25745,7 +25663,7 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="85"/>
       <c r="B3" s="70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C3" s="70"/>
       <c r="D3" s="70"/>
@@ -25775,11 +25693,11 @@
     <row r="5" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="85"/>
       <c r="B5" s="72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="85"/>
       <c r="D5" s="73" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E5" s="74"/>
       <c r="F5" s="75"/>
@@ -25807,11 +25725,11 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="85"/>
       <c r="B7" s="77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="85"/>
       <c r="D7" s="73" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E7" s="74"/>
       <c r="F7" s="75"/>
@@ -25839,7 +25757,7 @@
     <row r="9" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85"/>
       <c r="B9" s="77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="217">
@@ -25871,58 +25789,58 @@
     </row>
     <row r="11" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="85"/>
-      <c r="B11" s="256" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="256"/>
-      <c r="D11" s="256"/>
+      <c r="B11" s="250" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="250"/>
+      <c r="D11" s="250"/>
       <c r="E11" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="G11" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="79" t="s">
+      <c r="I11" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="J11" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="79" t="s">
-        <v>34</v>
-      </c>
       <c r="K11" s="79" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L11" s="85"/>
     </row>
     <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="85"/>
-      <c r="B12" s="264" t="s">
+      <c r="B12" s="251" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="251"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="257" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" s="258"/>
+      <c r="G12" s="258"/>
+      <c r="H12" s="258"/>
+      <c r="I12" s="258"/>
+      <c r="J12" s="258"/>
+      <c r="K12" s="259"/>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="264"/>
-      <c r="D12" s="264"/>
-      <c r="E12" s="249" t="s">
-        <v>349</v>
-      </c>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="250"/>
-      <c r="J12" s="250"/>
-      <c r="K12" s="251"/>
-      <c r="L12" s="85"/>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="265" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="265"/>
-      <c r="D13" s="265"/>
+      <c r="C13" s="252"/>
+      <c r="D13" s="252"/>
       <c r="E13" s="231">
         <v>0</v>
       </c>
@@ -25947,12 +25865,12 @@
       <c r="L13" s="85"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="265" t="str">
+      <c r="B14" s="252" t="str">
         <f>+'FORM INGRESOS'!A17</f>
         <v>Déficit Tarifario</v>
       </c>
-      <c r="C14" s="265"/>
-      <c r="D14" s="265"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="252"/>
       <c r="E14" s="232">
         <v>0</v>
       </c>
@@ -25977,12 +25895,12 @@
       <c r="L14" s="85"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="265" t="str">
+      <c r="B15" s="252" t="str">
         <f>+'FORM INGRESOS'!A19</f>
         <v>Subsidios (Informativo)</v>
       </c>
-      <c r="C15" s="265"/>
-      <c r="D15" s="265"/>
+      <c r="C15" s="252"/>
+      <c r="D15" s="252"/>
       <c r="E15" s="232">
         <v>0</v>
       </c>
@@ -26007,12 +25925,12 @@
       <c r="L15" s="85"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="265" t="str">
+      <c r="B16" s="252" t="str">
         <f>+'FORM INGRESOS'!A18</f>
         <v>Intereses Ganados</v>
       </c>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
+      <c r="C16" s="252"/>
+      <c r="D16" s="252"/>
       <c r="E16" s="232">
         <v>0</v>
       </c>
@@ -26037,12 +25955,12 @@
       <c r="L16" s="85"/>
     </row>
     <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="265" t="str">
+      <c r="B17" s="252" t="str">
         <f>+'FORM INGRESOS'!A20</f>
         <v>OTROS INGRESOS NO OPERATIVOS</v>
       </c>
-      <c r="C17" s="265"/>
-      <c r="D17" s="265"/>
+      <c r="C17" s="252"/>
+      <c r="D17" s="252"/>
       <c r="E17" s="232">
         <v>0</v>
       </c>
@@ -26067,11 +25985,11 @@
       <c r="L17" s="85"/>
     </row>
     <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="262" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="262"/>
-      <c r="D18" s="262"/>
+      <c r="B18" s="253" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="253"/>
+      <c r="D18" s="253"/>
       <c r="E18" s="230">
         <f>+E13-E14-E15+E16+E17</f>
         <v>0</v>
@@ -26103,11 +26021,11 @@
       <c r="L18" s="85"/>
     </row>
     <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="265" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="265"/>
-      <c r="D19" s="265"/>
+      <c r="B19" s="252" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="252"/>
+      <c r="D19" s="252"/>
       <c r="E19" s="231"/>
       <c r="F19" s="231"/>
       <c r="G19" s="231"/>
@@ -26118,11 +26036,11 @@
       <c r="L19" s="85"/>
     </row>
     <row r="20" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="261" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="261"/>
-      <c r="D20" s="261"/>
+      <c r="B20" s="254" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="254"/>
+      <c r="D20" s="254"/>
       <c r="E20" s="231"/>
       <c r="F20" s="231"/>
       <c r="G20" s="231"/>
@@ -26134,7 +26052,7 @@
     </row>
     <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="255" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="255"/>
       <c r="D21" s="255"/>
@@ -26163,7 +26081,7 @@
     </row>
     <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="255" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="255"/>
       <c r="D22" s="255"/>
@@ -26191,40 +26109,40 @@
       <c r="L22" s="85"/>
     </row>
     <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="257" t="s">
+      <c r="B23" s="249" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="249"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="232">
+        <v>0</v>
+      </c>
+      <c r="F23" s="232">
+        <v>0</v>
+      </c>
+      <c r="G23" s="232">
+        <v>0</v>
+      </c>
+      <c r="H23" s="232">
+        <v>0</v>
+      </c>
+      <c r="I23" s="232">
+        <v>0</v>
+      </c>
+      <c r="J23" s="232">
+        <v>0</v>
+      </c>
+      <c r="K23" s="232">
+        <v>0</v>
+      </c>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="254" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="257"/>
-      <c r="D23" s="257"/>
-      <c r="E23" s="232">
-        <v>0</v>
-      </c>
-      <c r="F23" s="232">
-        <v>0</v>
-      </c>
-      <c r="G23" s="232">
-        <v>0</v>
-      </c>
-      <c r="H23" s="232">
-        <v>0</v>
-      </c>
-      <c r="I23" s="232">
-        <v>0</v>
-      </c>
-      <c r="J23" s="232">
-        <v>0</v>
-      </c>
-      <c r="K23" s="232">
-        <v>0</v>
-      </c>
-      <c r="L23" s="85"/>
-    </row>
-    <row r="24" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="261" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="261"/>
-      <c r="D24" s="261"/>
+      <c r="C24" s="254"/>
+      <c r="D24" s="254"/>
       <c r="E24" s="232"/>
       <c r="F24" s="232"/>
       <c r="G24" s="232"/>
@@ -26236,7 +26154,7 @@
     </row>
     <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="255" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C25" s="255"/>
       <c r="D25" s="255"/>
@@ -26264,11 +26182,11 @@
       <c r="L25" s="85"/>
     </row>
     <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="257" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="257"/>
-      <c r="D26" s="257"/>
+      <c r="B26" s="249" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="249"/>
+      <c r="D26" s="249"/>
       <c r="E26" s="232">
         <v>0</v>
       </c>
@@ -26293,9 +26211,9 @@
       <c r="L26" s="85"/>
     </row>
     <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="257"/>
-      <c r="C27" s="257"/>
-      <c r="D27" s="257"/>
+      <c r="B27" s="249"/>
+      <c r="C27" s="249"/>
+      <c r="D27" s="249"/>
       <c r="E27" s="232"/>
       <c r="F27" s="232"/>
       <c r="G27" s="232"/>
@@ -26306,69 +26224,69 @@
       <c r="L27" s="85"/>
     </row>
     <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="249" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="232">
+        <v>0</v>
+      </c>
+      <c r="F28" s="232">
+        <v>0</v>
+      </c>
+      <c r="G28" s="232">
+        <v>0</v>
+      </c>
+      <c r="H28" s="232">
+        <v>0</v>
+      </c>
+      <c r="I28" s="232">
+        <v>0</v>
+      </c>
+      <c r="J28" s="232">
+        <v>0</v>
+      </c>
+      <c r="K28" s="232">
+        <v>0</v>
+      </c>
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="249" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="257"/>
-      <c r="D28" s="257"/>
-      <c r="E28" s="232">
-        <v>0</v>
-      </c>
-      <c r="F28" s="232">
-        <v>0</v>
-      </c>
-      <c r="G28" s="232">
-        <v>0</v>
-      </c>
-      <c r="H28" s="232">
-        <v>0</v>
-      </c>
-      <c r="I28" s="232">
-        <v>0</v>
-      </c>
-      <c r="J28" s="232">
-        <v>0</v>
-      </c>
-      <c r="K28" s="232">
-        <v>0</v>
-      </c>
-      <c r="L28" s="85"/>
-    </row>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="257" t="s">
+      <c r="C29" s="249"/>
+      <c r="D29" s="249"/>
+      <c r="E29" s="232">
+        <v>0</v>
+      </c>
+      <c r="F29" s="232">
+        <v>0</v>
+      </c>
+      <c r="G29" s="232">
+        <v>0</v>
+      </c>
+      <c r="H29" s="232">
+        <v>0</v>
+      </c>
+      <c r="I29" s="232">
+        <v>0</v>
+      </c>
+      <c r="J29" s="232">
+        <v>0</v>
+      </c>
+      <c r="K29" s="232">
+        <v>0</v>
+      </c>
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="253" t="s">
         <v>148</v>
       </c>
-      <c r="C29" s="257"/>
-      <c r="D29" s="257"/>
-      <c r="E29" s="232">
-        <v>0</v>
-      </c>
-      <c r="F29" s="232">
-        <v>0</v>
-      </c>
-      <c r="G29" s="232">
-        <v>0</v>
-      </c>
-      <c r="H29" s="232">
-        <v>0</v>
-      </c>
-      <c r="I29" s="232">
-        <v>0</v>
-      </c>
-      <c r="J29" s="232">
-        <v>0</v>
-      </c>
-      <c r="K29" s="232">
-        <v>0</v>
-      </c>
-      <c r="L29" s="85"/>
-    </row>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="262" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="262"/>
-      <c r="D30" s="262"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="253"/>
       <c r="E30" s="230">
         <f>SUM(E19:E29)</f>
         <v>0</v>
@@ -26400,11 +26318,11 @@
       <c r="L30" s="85"/>
     </row>
     <row r="31" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="263" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" s="263"/>
-      <c r="D31" s="263"/>
+      <c r="B31" s="256" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="256"/>
+      <c r="D31" s="256"/>
       <c r="E31" s="230">
         <f>+E18-E30</f>
         <v>0</v>
@@ -26436,11 +26354,11 @@
       <c r="L31" s="85"/>
     </row>
     <row r="32" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="264" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" s="264"/>
-      <c r="D32" s="264"/>
+      <c r="B32" s="251" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="251"/>
+      <c r="D32" s="251"/>
       <c r="E32" s="210"/>
       <c r="F32" s="210"/>
       <c r="G32" s="210"/>
@@ -26451,11 +26369,11 @@
       <c r="L32" s="85"/>
     </row>
     <row r="33" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="261" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="261"/>
-      <c r="D33" s="261"/>
+      <c r="B33" s="254" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="254"/>
+      <c r="D33" s="254"/>
       <c r="E33" s="211"/>
       <c r="F33" s="211"/>
       <c r="G33" s="211"/>
@@ -26467,7 +26385,7 @@
     </row>
     <row r="34" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="255" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C34" s="255"/>
       <c r="D34" s="255"/>
@@ -26496,7 +26414,7 @@
     </row>
     <row r="35" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="255" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="255"/>
       <c r="D35" s="255"/>
@@ -26524,9 +26442,9 @@
       <c r="L35" s="85"/>
     </row>
     <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="258"/>
-      <c r="C36" s="259"/>
-      <c r="D36" s="260"/>
+      <c r="B36" s="263"/>
+      <c r="C36" s="264"/>
+      <c r="D36" s="265"/>
       <c r="E36" s="232"/>
       <c r="F36" s="232"/>
       <c r="G36" s="232"/>
@@ -26537,11 +26455,11 @@
       <c r="L36" s="85"/>
     </row>
     <row r="37" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="261" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="261"/>
-      <c r="D37" s="261"/>
+      <c r="B37" s="254" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="254"/>
+      <c r="D37" s="254"/>
       <c r="E37" s="232"/>
       <c r="F37" s="232"/>
       <c r="G37" s="232"/>
@@ -26553,7 +26471,7 @@
     </row>
     <row r="38" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="255" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="255"/>
       <c r="D38" s="255"/>
@@ -26582,7 +26500,7 @@
     </row>
     <row r="39" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="255" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C39" s="255"/>
       <c r="D39" s="255"/>
@@ -26610,11 +26528,11 @@
       <c r="L39" s="85"/>
     </row>
     <row r="40" spans="2:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="253" t="s">
-        <v>189</v>
-      </c>
-      <c r="C40" s="254"/>
-      <c r="D40" s="254"/>
+      <c r="B40" s="261" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="262"/>
+      <c r="D40" s="262"/>
       <c r="E40" s="232"/>
       <c r="F40" s="232"/>
       <c r="G40" s="232"/>
@@ -26625,8 +26543,8 @@
       <c r="L40" s="85"/>
     </row>
     <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="257" t="s">
-        <v>153</v>
+      <c r="B41" s="249" t="s">
+        <v>152</v>
       </c>
       <c r="C41" s="255"/>
       <c r="D41" s="255"/>
@@ -26654,8 +26572,8 @@
       <c r="L41" s="85"/>
     </row>
     <row r="42" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="257" t="s">
-        <v>154</v>
+      <c r="B42" s="249" t="s">
+        <v>153</v>
       </c>
       <c r="C42" s="255"/>
       <c r="D42" s="255"/>
@@ -26683,7 +26601,7 @@
       <c r="L42" s="85"/>
     </row>
     <row r="43" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="257"/>
+      <c r="B43" s="249"/>
       <c r="C43" s="255"/>
       <c r="D43" s="255"/>
       <c r="E43" s="232"/>
@@ -26696,11 +26614,11 @@
       <c r="L43" s="85"/>
     </row>
     <row r="44" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="253" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="254"/>
-      <c r="D44" s="254"/>
+      <c r="B44" s="261" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="262"/>
+      <c r="D44" s="262"/>
       <c r="E44" s="232"/>
       <c r="F44" s="232"/>
       <c r="G44" s="232"/>
@@ -26712,7 +26630,7 @@
     </row>
     <row r="45" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="255" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C45" s="255"/>
       <c r="D45" s="255"/>
@@ -26741,7 +26659,7 @@
     </row>
     <row r="46" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="255" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46" s="255"/>
       <c r="D46" s="255"/>
@@ -26770,7 +26688,7 @@
     </row>
     <row r="47" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="255" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47" s="255"/>
       <c r="D47" s="255"/>
@@ -26798,11 +26716,11 @@
       <c r="L47" s="85"/>
     </row>
     <row r="48" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="256" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="256"/>
-      <c r="D48" s="256"/>
+      <c r="B48" s="250" t="s">
+        <v>158</v>
+      </c>
+      <c r="C48" s="250"/>
+      <c r="D48" s="250"/>
       <c r="E48" s="230">
         <f>SUM(E33:E47)</f>
         <v>0</v>
@@ -26847,18 +26765,18 @@
       <c r="L49" s="87"/>
     </row>
     <row r="50" spans="1:30" s="83" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="252" t="s">
-        <v>276</v>
-      </c>
-      <c r="C50" s="252"/>
-      <c r="D50" s="252"/>
-      <c r="E50" s="252"/>
-      <c r="F50" s="252"/>
-      <c r="G50" s="252"/>
-      <c r="H50" s="252"/>
-      <c r="I50" s="252"/>
-      <c r="J50" s="252"/>
-      <c r="K50" s="252"/>
+      <c r="B50" s="260" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="260"/>
+      <c r="D50" s="260"/>
+      <c r="E50" s="260"/>
+      <c r="F50" s="260"/>
+      <c r="G50" s="260"/>
+      <c r="H50" s="260"/>
+      <c r="I50" s="260"/>
+      <c r="J50" s="260"/>
+      <c r="K50" s="260"/>
       <c r="L50" s="88"/>
       <c r="M50" s="84"/>
       <c r="N50" s="84"/>
@@ -26898,30 +26816,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="E12:K12"/>
     <mergeCell ref="B50:K50"/>
     <mergeCell ref="B44:D44"/>
@@ -26938,6 +26832,30 @@
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -27667,50 +27585,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="138" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="256"/>
+      <c r="A1" s="250" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="250"/>
+      <c r="C1" s="250" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="250"/>
       <c r="E1" s="79" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F1" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="H1" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="79" t="s">
+      <c r="J1" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="79" t="s">
+      <c r="K1" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="79" t="s">
-        <v>34</v>
-      </c>
       <c r="L1" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M1" s="137"/>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="270" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="270"/>
+      <c r="C2" s="270" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="270" t="s">
         <v>123</v>
-      </c>
-      <c r="B2" s="267"/>
-      <c r="C2" s="267" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="267" t="s">
-        <v>124</v>
       </c>
       <c r="E2" s="209" cm="1">
         <f t="array" ref="E2">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A2:A2)</f>
@@ -27740,12 +27658,12 @@
       <c r="M2" s="91"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="267" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="267"/>
-      <c r="C3" s="267"/>
-      <c r="D3" s="267"/>
+      <c r="A3" s="270" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="270"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
       <c r="E3" s="209" cm="1">
         <f t="array" ref="E3">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A3:A3)</f>
         <v>0</v>
@@ -27774,14 +27692,14 @@
       <c r="M3" s="91"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="267" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="267"/>
-      <c r="C4" s="267" t="s">
+      <c r="A4" s="270" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="270"/>
+      <c r="C4" s="270" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="267"/>
+      <c r="D4" s="270"/>
       <c r="E4" s="209" cm="1">
         <f t="array" ref="E4">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A4:A4)</f>
         <v>0</v>
@@ -27810,12 +27728,12 @@
       <c r="M4" s="91"/>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="267" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="267"/>
-      <c r="C5" s="267"/>
-      <c r="D5" s="267"/>
+      <c r="A5" s="270" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="270"/>
+      <c r="C5" s="270"/>
+      <c r="D5" s="270"/>
       <c r="E5" s="209" cm="1">
         <f t="array" ref="E5">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A5:A5)</f>
         <v>0</v>
@@ -27844,12 +27762,12 @@
       <c r="M5" s="91"/>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="267" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="267"/>
-      <c r="C6" s="267"/>
-      <c r="D6" s="267"/>
+      <c r="A6" s="270" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="270"/>
+      <c r="C6" s="270"/>
+      <c r="D6" s="270"/>
       <c r="E6" s="209" cm="1">
         <f t="array" ref="E6">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A6:A6)</f>
         <v>0</v>
@@ -27878,14 +27796,14 @@
       <c r="M6" s="91"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="267" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="267"/>
+      <c r="A7" s="270" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="270"/>
       <c r="C7" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="267"/>
+      <c r="D7" s="270"/>
       <c r="E7" s="209" cm="1">
         <f t="array" ref="E7">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A7:A7)</f>
         <v>0</v>
@@ -27914,10 +27832,10 @@
       <c r="M7" s="91"/>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="267" t="s">
+      <c r="A8" s="270" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="267"/>
+      <c r="B8" s="270"/>
       <c r="C8" s="132" t="s">
         <v>6</v>
       </c>
@@ -27952,15 +27870,15 @@
       <c r="M8" s="91"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="267" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="267"/>
+      <c r="A9" s="270" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="270"/>
       <c r="C9" s="132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" s="132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="209" cm="1">
         <f t="array" ref="E9">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A9:A9)</f>
@@ -27990,12 +27908,12 @@
       <c r="M9" s="91"/>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="266" t="s">
-        <v>295</v>
-      </c>
-      <c r="B10" s="266"/>
-      <c r="C10" s="266"/>
-      <c r="D10" s="266"/>
+      <c r="A10" s="271" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" s="271"/>
+      <c r="C10" s="271"/>
+      <c r="D10" s="271"/>
       <c r="E10" s="208">
         <f>SUM(E2:E9)</f>
         <v>0</v>
@@ -28046,22 +27964,22 @@
       <c r="M11" s="91"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="268" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="269"/>
+      <c r="A12" s="266" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="267"/>
       <c r="C12" s="229">
         <v>0</v>
       </c>
       <c r="D12" s="133"/>
       <c r="E12" s="134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F12" s="134"/>
       <c r="G12" s="134"/>
       <c r="H12" s="134"/>
       <c r="I12" s="134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J12" s="134"/>
       <c r="K12" s="134"/>
@@ -28069,10 +27987,10 @@
       <c r="M12" s="141"/>
     </row>
     <row r="13" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="270" t="s">
-        <v>351</v>
-      </c>
-      <c r="B13" s="271"/>
+      <c r="A13" s="268" t="s">
+        <v>347</v>
+      </c>
+      <c r="B13" s="269"/>
       <c r="C13" s="230">
         <f>+C12+K10</f>
         <v>0</v>
@@ -28116,11 +28034,19 @@
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C23" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A2:B2"/>
@@ -28129,14 +28055,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="El dato ingresado debe ser numérico y mayor y positivo." sqref="F2:F9 H2:L9 C12" xr:uid="{00000000-0002-0000-0800-000000000000}">
@@ -28867,83 +28785,59 @@
   <sheetData>
     <row r="1" spans="1:13" s="155" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="153" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="154" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="154" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="154" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="154" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="154" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="154" t="s">
+      <c r="J1" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="154" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="154" t="s">
+      <c r="K1" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="154" t="s">
+      <c r="L1" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="154" t="s">
-        <v>34</v>
-      </c>
       <c r="M1" s="154" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="156" t="s">
-        <v>316</v>
-      </c>
-      <c r="B2" s="223">
-        <v>1002945</v>
-      </c>
+      <c r="A2" s="156"/>
+      <c r="B2" s="223"/>
       <c r="C2" s="156"/>
-      <c r="D2" s="157" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="224" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="145" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="233">
-        <v>20000</v>
-      </c>
-      <c r="H2" s="233">
-        <v>0</v>
-      </c>
-      <c r="I2" s="233">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="233">
-        <v>5000</v>
-      </c>
-      <c r="K2" s="233">
-        <v>5000</v>
-      </c>
-      <c r="L2" s="233">
-        <v>2100</v>
-      </c>
-      <c r="M2" s="233">
-        <v>2100</v>
-      </c>
+      <c r="D2" s="157"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="M2" s="233"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="156"/>
@@ -33223,378 +33117,259 @@
   <sheetData>
     <row r="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1" s="153" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="D1" s="153" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="153" t="s">
+      <c r="F1" s="153" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="153" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="153" t="s">
+      <c r="H1" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="153" t="s">
+      <c r="I1" s="153" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="154" t="s">
         <v>296</v>
       </c>
-      <c r="G1" s="163" t="s">
+      <c r="N1" s="153" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="153" t="s">
+        <v>348</v>
+      </c>
+      <c r="P1" s="153" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q1" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="153" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="153" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="154" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="154" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="154" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="154" t="s">
-        <v>297</v>
-      </c>
-      <c r="N1" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="153" t="s">
-        <v>352</v>
-      </c>
-      <c r="P1" s="153" t="s">
+      <c r="R1" s="164" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="153" t="s">
-        <v>92</v>
-      </c>
-      <c r="R1" s="164" t="s">
+      <c r="S1" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="154" t="s">
+      <c r="T1" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="153" t="s">
+      <c r="U1" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="U1" s="153" t="s">
+      <c r="V1" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="V1" s="153" t="s">
+      <c r="W1" s="153" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="153" t="s">
+      <c r="X1" s="153" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y1" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="X1" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y1" s="153" t="s">
+      <c r="Z1" s="153" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA1" s="153" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="153" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD1" s="153" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="154" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="154" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="154" t="s">
+        <v>298</v>
+      </c>
+      <c r="AH1" s="153" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI1" s="153" t="s">
         <v>49</v>
       </c>
-      <c r="Z1" s="153" t="s">
-        <v>300</v>
-      </c>
-      <c r="AA1" s="153" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB1" s="153" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC1" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD1" s="153" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE1" s="154" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF1" s="154" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG1" s="154" t="s">
-        <v>299</v>
-      </c>
-      <c r="AH1" s="153" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI1" s="153" t="s">
+      <c r="AJ1" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" s="153" t="s">
+      <c r="AK1" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="AK1" s="153" t="s">
+      <c r="AL1" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" s="153" t="s">
+      <c r="AM1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="AM1" s="153" t="s">
+      <c r="AN1" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" s="153" t="s">
+      <c r="AO1" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="AO1" s="153" t="s">
+      <c r="AP1" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="AP1" s="153" t="s">
+      <c r="AQ1" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="AQ1" s="153" t="s">
+      <c r="AR1" s="153" t="s">
         <v>58</v>
       </c>
-      <c r="AR1" s="153" t="s">
+      <c r="AS1" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="AS1" s="153" t="s">
+      <c r="AT1" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="AT1" s="153" t="s">
+      <c r="AU1" s="153" t="s">
         <v>61</v>
       </c>
-      <c r="AU1" s="153" t="s">
+      <c r="AV1" s="153" t="s">
         <v>62</v>
       </c>
-      <c r="AV1" s="153" t="s">
+      <c r="AW1" s="153" t="s">
         <v>63</v>
       </c>
-      <c r="AW1" s="153" t="s">
+      <c r="AX1" s="153" t="s">
         <v>64</v>
       </c>
-      <c r="AX1" s="153" t="s">
+      <c r="AY1" s="153" t="s">
         <v>65</v>
       </c>
-      <c r="AY1" s="153" t="s">
+      <c r="AZ1" s="153" t="s">
         <v>66</v>
       </c>
-      <c r="AZ1" s="153" t="s">
+      <c r="BA1" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="BA1" s="153" t="s">
+      <c r="BB1" s="153" t="s">
         <v>68</v>
       </c>
-      <c r="BB1" s="153" t="s">
+      <c r="BC1" s="153" t="s">
         <v>69</v>
       </c>
-      <c r="BC1" s="153" t="s">
+      <c r="BD1" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="BD1" s="153" t="s">
+      <c r="BE1" s="153" t="s">
         <v>71</v>
       </c>
-      <c r="BE1" s="153" t="s">
+      <c r="BF1" s="153" t="s">
         <v>72</v>
       </c>
-      <c r="BF1" s="153" t="s">
+      <c r="BG1" s="153" t="s">
         <v>73</v>
       </c>
-      <c r="BG1" s="153" t="s">
+      <c r="BH1" s="153" t="s">
         <v>74</v>
       </c>
-      <c r="BH1" s="153" t="s">
+      <c r="BI1" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="BI1" s="153" t="s">
+      <c r="BJ1" s="153" t="s">
         <v>76</v>
       </c>
-      <c r="BJ1" s="153" t="s">
+      <c r="BK1" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="BK1" s="153" t="s">
+      <c r="BL1" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="BL1" s="153" t="s">
+      <c r="BM1" s="153" t="s">
         <v>79</v>
       </c>
-      <c r="BM1" s="153" t="s">
+      <c r="BN1" s="153" t="s">
         <v>80</v>
       </c>
-      <c r="BN1" s="153" t="s">
+      <c r="BO1" s="153" t="s">
+        <v>302</v>
+      </c>
+      <c r="BP1" s="153" t="s">
         <v>81</v>
       </c>
-      <c r="BO1" s="153" t="s">
-        <v>303</v>
-      </c>
-      <c r="BP1" s="153" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A2" s="156" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="148" t="s">
-        <v>318</v>
-      </c>
-      <c r="C2" s="148" t="s">
-        <v>318</v>
-      </c>
-      <c r="D2" s="165">
-        <v>2026</v>
-      </c>
-      <c r="F2" s="234" t="s">
-        <v>319</v>
-      </c>
-      <c r="M2" s="148" t="s">
-        <v>318</v>
-      </c>
-      <c r="N2" s="157" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="148" t="s">
-        <v>272</v>
-      </c>
-      <c r="P2" s="148" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="150" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="152">
-        <f>+IF($Q2="No iniciado 0%",0%,IF($Q2="Elaboración de pliegos 5%",5%,IF($Q2="Disponibilidad de pliegos 10%",10%,IF($Q2="Publicación del proceso 15%",15%,IF($Q2="Resolución de adjudicación 30%",30%,IF($Q2="Adjudicación y firma de contrato 40%",40%,IF($Q2="En ejecución 41% - 90%",(40%+($R2*50%)),IF($Q2="Acta de entrega - recepción 95%",IF($R2=100%,95%,""),IF($Q2="Registro contable 100%",IF($R2=100%,100%,""),"")))))))))</f>
-        <v>0</v>
-      </c>
+      <c r="A2" s="156"/>
+      <c r="D2" s="165"/>
+      <c r="F2" s="234"/>
+      <c r="N2" s="157"/>
       <c r="W2" s="166"/>
-      <c r="X2" s="235">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="235">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="235">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BC2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BE2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BF2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BG2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BH2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="235">
-        <v>0</v>
-      </c>
-      <c r="BK2" s="148" t="s">
-        <v>25</v>
-      </c>
-      <c r="BL2" s="237">
-        <v>46023</v>
-      </c>
-      <c r="BM2" s="237">
-        <v>46023</v>
-      </c>
-      <c r="BN2" s="236">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="236">
-        <v>0</v>
-      </c>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
+      <c r="AD2" s="235"/>
+      <c r="AE2" s="235"/>
+      <c r="AF2" s="235"/>
+      <c r="AG2" s="235"/>
+      <c r="AH2" s="235"/>
+      <c r="AI2" s="235"/>
+      <c r="AJ2" s="235"/>
+      <c r="AK2" s="235"/>
+      <c r="AL2" s="235"/>
+      <c r="AM2" s="235"/>
+      <c r="AN2" s="235"/>
+      <c r="AO2" s="235"/>
+      <c r="AP2" s="235"/>
+      <c r="AQ2" s="235"/>
+      <c r="AR2" s="235"/>
+      <c r="AS2" s="235"/>
+      <c r="AT2" s="235"/>
+      <c r="AU2" s="235"/>
+      <c r="AV2" s="235"/>
+      <c r="AW2" s="235"/>
+      <c r="AX2" s="235"/>
+      <c r="AY2" s="235"/>
+      <c r="AZ2" s="235"/>
+      <c r="BA2" s="235"/>
+      <c r="BB2" s="235"/>
+      <c r="BC2" s="235"/>
+      <c r="BD2" s="235"/>
+      <c r="BE2" s="235"/>
+      <c r="BF2" s="235"/>
+      <c r="BG2" s="235"/>
+      <c r="BH2" s="235"/>
+      <c r="BI2" s="235"/>
+      <c r="BJ2" s="235"/>
+      <c r="BL2" s="237"/>
+      <c r="BM2" s="237"/>
+      <c r="BN2" s="236"/>
+      <c r="BO2" s="236"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -33705,206 +33480,199 @@
   <sheetData>
     <row r="1" spans="1:64" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="153" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="153" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="153" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D1" s="153" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>296</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="153" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="153" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="153" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="154" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="154" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="154" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="154" t="s">
-        <v>297</v>
-      </c>
-      <c r="K1" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="153" t="s">
+      <c r="N1" s="164" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="153" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="164" t="s">
+      <c r="O1" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="167" t="s">
+      <c r="P1" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="153" t="s">
+      <c r="Q1" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="153" t="s">
+      <c r="R1" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="153" t="s">
-        <v>47</v>
-      </c>
       <c r="S1" s="153" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T1" s="153" t="s">
+        <v>48</v>
+      </c>
+      <c r="U1" s="153" t="s">
+        <v>299</v>
+      </c>
+      <c r="V1" s="153" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="153" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="153" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="154" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC1" s="153" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD1" s="153" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="153" t="s">
-        <v>300</v>
-      </c>
-      <c r="V1" s="153" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="153" t="s">
-        <v>31</v>
-      </c>
-      <c r="X1" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y1" s="153" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="154" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="154" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB1" s="154" t="s">
-        <v>299</v>
-      </c>
-      <c r="AC1" s="153" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="153" t="s">
+      <c r="AE1" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="153" t="s">
+      <c r="AF1" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="AF1" s="153" t="s">
+      <c r="AG1" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="AG1" s="153" t="s">
+      <c r="AH1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="AH1" s="153" t="s">
+      <c r="AI1" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="AI1" s="153" t="s">
+      <c r="AJ1" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="AJ1" s="153" t="s">
+      <c r="AK1" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="153" t="s">
+      <c r="AL1" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="AL1" s="153" t="s">
+      <c r="AM1" s="153" t="s">
         <v>58</v>
       </c>
-      <c r="AM1" s="153" t="s">
+      <c r="AN1" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="AN1" s="153" t="s">
+      <c r="AO1" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="AO1" s="153" t="s">
+      <c r="AP1" s="153" t="s">
         <v>61</v>
       </c>
-      <c r="AP1" s="153" t="s">
+      <c r="AQ1" s="153" t="s">
         <v>62</v>
       </c>
-      <c r="AQ1" s="153" t="s">
+      <c r="AR1" s="153" t="s">
         <v>63</v>
       </c>
-      <c r="AR1" s="153" t="s">
+      <c r="AS1" s="153" t="s">
         <v>64</v>
       </c>
-      <c r="AS1" s="153" t="s">
+      <c r="AT1" s="153" t="s">
         <v>65</v>
       </c>
-      <c r="AT1" s="153" t="s">
+      <c r="AU1" s="153" t="s">
         <v>66</v>
       </c>
-      <c r="AU1" s="153" t="s">
+      <c r="AV1" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="AV1" s="153" t="s">
+      <c r="AW1" s="153" t="s">
         <v>68</v>
       </c>
-      <c r="AW1" s="153" t="s">
+      <c r="AX1" s="153" t="s">
         <v>69</v>
       </c>
-      <c r="AX1" s="153" t="s">
+      <c r="AY1" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="AY1" s="153" t="s">
+      <c r="AZ1" s="153" t="s">
         <v>71</v>
       </c>
-      <c r="AZ1" s="153" t="s">
+      <c r="BA1" s="153" t="s">
         <v>72</v>
       </c>
-      <c r="BA1" s="153" t="s">
+      <c r="BB1" s="153" t="s">
         <v>73</v>
       </c>
-      <c r="BB1" s="153" t="s">
+      <c r="BC1" s="153" t="s">
         <v>74</v>
       </c>
-      <c r="BC1" s="153" t="s">
+      <c r="BD1" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="BD1" s="153" t="s">
+      <c r="BE1" s="153" t="s">
         <v>76</v>
       </c>
-      <c r="BE1" s="153" t="s">
+      <c r="BF1" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="BF1" s="153" t="s">
-        <v>78</v>
-      </c>
       <c r="BG1" s="153" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH1" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="BH1" s="153" t="s">
-        <v>84</v>
-      </c>
       <c r="BI1" s="153" t="s">
+        <v>80</v>
+      </c>
+      <c r="BJ1" s="153" t="s">
+        <v>302</v>
+      </c>
+      <c r="BK1" s="153" t="s">
         <v>81</v>
       </c>
-      <c r="BJ1" s="153" t="s">
-        <v>303</v>
-      </c>
-      <c r="BK1" s="153" t="s">
-        <v>82</v>
-      </c>
       <c r="BL1" s="168"/>
     </row>
     <row r="2" spans="1:64" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="241" t="s">
-        <v>317</v>
-      </c>
-      <c r="B2" s="148" t="s">
-        <v>355</v>
-      </c>
-      <c r="C2" s="169">
-        <v>2026</v>
-      </c>
+      <c r="A2" s="241"/>
+      <c r="C2" s="169"/>
       <c r="D2" s="170"/>
       <c r="E2" s="171"/>
       <c r="F2" s="149"/>
@@ -33915,145 +33683,54 @@
       <c r="L2" s="149"/>
       <c r="M2" s="149"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="152" t="str">
-        <f>+IF($M2="No iniciado 0%",0%,IF($M2="Elaboración de pliegos 5%",5%,IF($M2="Disponibilidad de pliegos 10%",10%,IF($M2="Publicación del proceso 15%",15%,IF($M2="Resolución de adjudicación 30%",30%,IF($M2="Adjudicación y firma de contrato 40%",40%,IF($M2="En ejecución 41% - 90%",(40%+($N2*50%)),IF($M2="Acta de entrega - recepción 95%",IF($N2=100%,95%,""),IF($M2="Registro contable 100%",IF($N2=100%,100%,""),"")))))))))</f>
-        <v/>
-      </c>
+      <c r="O2" s="152"/>
       <c r="P2" s="173"/>
       <c r="Q2" s="173"/>
       <c r="R2" s="149"/>
-      <c r="S2" s="238">
-        <v>0</v>
-      </c>
-      <c r="T2" s="238">
-        <v>0</v>
-      </c>
-      <c r="U2" s="238">
-        <v>0</v>
-      </c>
-      <c r="V2" s="238">
-        <v>0</v>
-      </c>
-      <c r="W2" s="238">
-        <v>0</v>
-      </c>
-      <c r="X2" s="238">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="238">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="238">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BC2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BE2" s="238">
-        <v>0</v>
-      </c>
-      <c r="BF2" s="174" t="s">
-        <v>25</v>
-      </c>
-      <c r="BG2" s="239">
-        <v>46023</v>
-      </c>
-      <c r="BH2" s="239">
-        <v>46023</v>
-      </c>
-      <c r="BI2" s="240">
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="240">
-        <v>0</v>
-      </c>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="238"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="238"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="238"/>
+      <c r="AJ2" s="238"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="238"/>
+      <c r="AM2" s="238"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="238"/>
+      <c r="AP2" s="238"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="238"/>
+      <c r="AS2" s="238"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="238"/>
+      <c r="AV2" s="238"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="238"/>
+      <c r="AY2" s="238"/>
+      <c r="AZ2" s="238"/>
+      <c r="BA2" s="238"/>
+      <c r="BB2" s="238"/>
+      <c r="BC2" s="238"/>
+      <c r="BD2" s="238"/>
+      <c r="BE2" s="238"/>
+      <c r="BF2" s="174"/>
+      <c r="BG2" s="239"/>
+      <c r="BH2" s="239"/>
+      <c r="BI2" s="240"/>
+      <c r="BJ2" s="240"/>
       <c r="BK2" s="176"/>
       <c r="BL2" s="177"/>
     </row>
@@ -34798,37 +34475,37 @@
   <sheetData>
     <row r="1" spans="1:10" s="180" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="178" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C1" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="E1" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="79" t="s">
+      <c r="G1" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="H1" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="79" t="s">
-        <v>34</v>
-      </c>
       <c r="I1" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J1" s="179"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="272">
         <f>+SUMIFS(recursos_aprobados[monto_aprobado],recursos_aprobados[servicio],"SAPG",recursos_aprobados[distribuidora],'FORM RESUMEN '!D5)</f>
@@ -34859,7 +34536,7 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="273"/>
       <c r="C3" s="207">
@@ -34887,7 +34564,7 @@
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="140" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B4" s="242">
         <f>SUM(B2)</f>
@@ -34937,7 +34614,7 @@
     </row>
     <row r="6" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="226" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="207">
         <v>0</v>
@@ -34953,7 +34630,7 @@
     </row>
     <row r="7" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="227" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B7" s="208">
         <f>+B6+H4</f>
@@ -35715,73 +35392,55 @@
   <sheetData>
     <row r="1" spans="1:12" s="155" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="153" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="154" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="154" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="154" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="154" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="154" t="s">
+      <c r="I1" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="154" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="154" t="s">
+      <c r="J1" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="154" t="s">
+      <c r="K1" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="154" t="s">
-        <v>34</v>
-      </c>
       <c r="L1" s="154" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="156" t="s">
-        <v>317</v>
-      </c>
-      <c r="B2" s="223">
-        <v>1410</v>
-      </c>
+      <c r="A2" s="156"/>
+      <c r="B2" s="223"/>
       <c r="C2" s="156"/>
       <c r="D2" s="144"/>
       <c r="E2" s="145"/>
-      <c r="F2" s="233">
-        <v>0</v>
-      </c>
-      <c r="G2" s="233">
-        <v>0</v>
-      </c>
-      <c r="H2" s="233">
-        <v>0</v>
-      </c>
-      <c r="I2" s="233">
-        <v>0</v>
-      </c>
-      <c r="J2" s="233">
-        <v>0</v>
-      </c>
-      <c r="K2" s="233">
-        <v>0</v>
-      </c>
-      <c r="L2" s="233">
-        <v>0</v>
-      </c>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="156"/>

--- a/Formularios de Control Ejecución Presupuestos_Proyectos.xlsx
+++ b/Formularios de Control Ejecución Presupuestos_Proyectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\william.boconzaca\Downloads\I\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexandra.falcon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4419C35A-47C7-4C6F-8616-4BFD1FD2A352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49F3BDF-B468-44F9-9C51-B066ED6EAEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-945" windowWidth="21840" windowHeight="13140" tabRatio="657" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="657" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listas" sheetId="50" state="hidden" r:id="rId1"/>
@@ -49,19 +49,32 @@
     <definedName name="Empresas" localSheetId="11">#REF!</definedName>
     <definedName name="Empresas">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2174,7 +2187,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="288">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2930,30 +2943,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="11" fillId="6" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2972,6 +2961,15 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2979,6 +2977,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2991,12 +3010,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="2" borderId="6" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3051,6 +3064,9 @@
     <xf numFmtId="0" fontId="11" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -3074,6 +3090,138 @@
     <cellStyle name="Porcentaje 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
   </cellStyles>
   <dxfs count="360">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3470,31 +3618,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4574,31 +4697,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5730,31 +5828,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -7749,33 +7822,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
@@ -7864,31 +7910,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -11986,76 +12007,78 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="estado_proyecto" dataDxfId="193"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="etapa_ejecucion_proyecto" dataDxfId="192"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="avance_ejecucion_fisica" dataDxfId="191" dataCellStyle="Porcentaje"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="avance_ejecucion_total" dataDxfId="190"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="fecha_inicio_proyecto" dataDxfId="189"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="fecha_pro_fin_proyecto" dataDxfId="188"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="fecha_fin_proyecto" dataDxfId="187"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="presupuesto_codificado_arrastre" dataDxfId="186" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="devengado_arrastre" dataDxfId="185" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="pagado_arrastre" dataDxfId="184" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="asignacion_inicial" dataDxfId="183" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0200-000016000000}" name="reformas" dataDxfId="182" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0200-000017000000}" name="presupuesto_codificado" dataDxfId="181" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0200-000018000000}" name="pre_compromiso" dataDxfId="180" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0200-000019000000}" name="compromiso" dataDxfId="179" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0200-00001A000000}" name="devengado" dataDxfId="178" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0200-00001B000000}" name="pagado" dataDxfId="177" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0200-00001C000000}" name="anticipo_no_amortizado" dataDxfId="176" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0200-00001D000000}" name="bd_planificado" dataDxfId="175" dataCellStyle="Millares"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0200-00001E000000}" name="bd_ejecutado" dataDxfId="174" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0200-00001F000000}" name="vcs_planificado" dataDxfId="173" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0200-000020000000}" name="vcs_ejecutado" dataDxfId="172" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0200-000021000000}" name="vss_planificado" dataDxfId="171" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0200-000022000000}" name="vss_ejecutado" dataDxfId="170" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0200-000023000000}" name="tv_planificado" dataDxfId="169" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0200-000024000000}" name="tv_ejecutado" dataDxfId="168" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0200-000025000000}" name="ln_planificado" dataDxfId="167" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0200-000026000000}" name="ln_ejecutado" dataDxfId="166" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0200-000027000000}" name="at_planificado" dataDxfId="165" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0200-000028000000}" name="at_ejecutado" dataDxfId="164" dataCellStyle="Millares"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0200-000029000000}" name="mt_planificado" dataDxfId="163" dataCellStyle="Millares"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0200-00002A000000}" name="mt_ejecutado" dataDxfId="162" dataCellStyle="Millares"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0200-00002B000000}" name="bt_planificado" dataDxfId="161" dataCellStyle="Millares"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0200-00002C000000}" name="bt_ejecutado" dataDxfId="160" dataCellStyle="Millares"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0200-00002D000000}" name="am_planificado" dataDxfId="159" dataCellStyle="Millares"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0200-00002E000000}" name="am_ejecutado" dataDxfId="158" dataCellStyle="Millares"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0200-00002F000000}" name="m_planificado" dataDxfId="157" dataCellStyle="Millares"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0200-000030000000}" name="m_ejecutado" dataDxfId="156" dataCellStyle="Millares"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0200-000031000000}" name="td_planificado" dataDxfId="155" dataCellStyle="Millares"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0200-000032000000}" name="td_ejecutado" dataDxfId="154" dataCellStyle="Millares"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0200-000033000000}" name="pitd_planificado" dataDxfId="153" dataCellStyle="Millares"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0200-000034000000}" name="pitd_ejecutado" dataDxfId="152" dataCellStyle="Millares"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0200-000035000000}" name="sdn_planificado" dataDxfId="151" dataCellStyle="Millares"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0200-000036000000}" name="sdn_ejecutado" dataDxfId="150" dataCellStyle="Millares"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0200-000037000000}" name="pisdn_planificado" dataDxfId="149" dataCellStyle="Millares"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0200-000038000000}" name="pisdn_ejecutado" dataDxfId="148" dataCellStyle="Millares"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0200-000039000000}" name="perm_amb" dataDxfId="147" dataCellStyle="Millares"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0200-00003A000000}" name="fecha_permiso_planif" dataDxfId="146" dataCellStyle="Millares 3"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0200-00003B000000}" name="fecha_permiso_ejec" dataDxfId="145" dataCellStyle="Millares 3"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0200-00003C000000}" name="empleos_generados" dataDxfId="144" dataCellStyle="Millares 3"/>
-    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0200-000041000000}" name="nro_personal_fem" dataDxfId="143" dataCellStyle="Millares 3"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0200-00003D000000}" name="observaciones" dataDxfId="142"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="avance_ejecucion_total" dataDxfId="4">
+      <calculatedColumnFormula>+IF($M2="No iniciado 0%",0%,IF($M2="Elaboración de pliegos 5%",5%,IF($M2="Disponibilidad de pliegos 10%",10%,IF($M2="Publicación del proceso 15%",15%,IF($M2="Resolución de adjudicación 30%",30%,IF($M2="Adjudicación y firma de contrato 40%",40%,IF($M2="En ejecución 41% - 90%",(40%+($N2*50%)),IF($M2="Acta de entrega - recepción 95%",IF($N2=100%,95%,""),IF($M2="Registro contable 100%",IF($N2=100%,100%,""),"")))))))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="fecha_inicio_proyecto" dataDxfId="190"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="fecha_pro_fin_proyecto" dataDxfId="189"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="fecha_fin_proyecto" dataDxfId="188"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="presupuesto_codificado_arrastre" dataDxfId="187" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="devengado_arrastre" dataDxfId="186" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="pagado_arrastre" dataDxfId="185" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="asignacion_inicial" dataDxfId="184" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0200-000016000000}" name="reformas" dataDxfId="0" dataCellStyle="Millares 3"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0200-000017000000}" name="presupuesto_codificado" dataDxfId="183" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0200-000018000000}" name="pre_compromiso" dataDxfId="182" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0200-000019000000}" name="compromiso" dataDxfId="181" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0200-00001A000000}" name="devengado" dataDxfId="180" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0200-00001B000000}" name="pagado" dataDxfId="179" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0200-00001C000000}" name="anticipo_no_amortizado" dataDxfId="178" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0200-00001D000000}" name="bd_planificado" dataDxfId="177" dataCellStyle="Millares"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0200-00001E000000}" name="bd_ejecutado" dataDxfId="176" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0200-00001F000000}" name="vcs_planificado" dataDxfId="175" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0200-000020000000}" name="vcs_ejecutado" dataDxfId="174" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0200-000021000000}" name="vss_planificado" dataDxfId="173" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0200-000022000000}" name="vss_ejecutado" dataDxfId="172" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0200-000023000000}" name="tv_planificado" dataDxfId="171" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0200-000024000000}" name="tv_ejecutado" dataDxfId="170" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0200-000025000000}" name="ln_planificado" dataDxfId="169" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0200-000026000000}" name="ln_ejecutado" dataDxfId="168" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0200-000027000000}" name="at_planificado" dataDxfId="167" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0200-000028000000}" name="at_ejecutado" dataDxfId="166" dataCellStyle="Millares"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0200-000029000000}" name="mt_planificado" dataDxfId="165" dataCellStyle="Millares"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0200-00002A000000}" name="mt_ejecutado" dataDxfId="164" dataCellStyle="Millares"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0200-00002B000000}" name="bt_planificado" dataDxfId="163" dataCellStyle="Millares"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0200-00002C000000}" name="bt_ejecutado" dataDxfId="162" dataCellStyle="Millares"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0200-00002D000000}" name="am_planificado" dataDxfId="161" dataCellStyle="Millares"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0200-00002E000000}" name="am_ejecutado" dataDxfId="160" dataCellStyle="Millares"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0200-00002F000000}" name="m_planificado" dataDxfId="159" dataCellStyle="Millares"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0200-000030000000}" name="m_ejecutado" dataDxfId="158" dataCellStyle="Millares"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0200-000031000000}" name="td_planificado" dataDxfId="157" dataCellStyle="Millares"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0200-000032000000}" name="td_ejecutado" dataDxfId="156" dataCellStyle="Millares"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0200-000033000000}" name="pitd_planificado" dataDxfId="155" dataCellStyle="Millares"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0200-000034000000}" name="pitd_ejecutado" dataDxfId="154" dataCellStyle="Millares"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0200-000035000000}" name="sdn_planificado" dataDxfId="153" dataCellStyle="Millares"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0200-000036000000}" name="sdn_ejecutado" dataDxfId="152" dataCellStyle="Millares"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0200-000037000000}" name="pisdn_planificado" dataDxfId="151" dataCellStyle="Millares"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0200-000038000000}" name="pisdn_ejecutado" dataDxfId="150" dataCellStyle="Millares"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0200-000039000000}" name="perm_amb" dataDxfId="149" dataCellStyle="Millares"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0200-00003A000000}" name="fecha_permiso_planif" dataDxfId="148" dataCellStyle="Millares 3"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0200-00003B000000}" name="fecha_permiso_ejec" dataDxfId="147" dataCellStyle="Millares 3"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0200-00003C000000}" name="empleos_generados" dataDxfId="146" dataCellStyle="Millares 3"/>
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0200-000041000000}" name="nro_personal_fem" dataDxfId="145" dataCellStyle="Millares 3"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0200-00003D000000}" name="observaciones" dataDxfId="144"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Detalle_AOM" displayName="Detalle_AOM" ref="A1:L2" totalsRowShown="0" headerRowDxfId="141" dataDxfId="140" dataCellStyle="Millares 3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Detalle_AOM" displayName="Detalle_AOM" ref="A1:L2" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142" dataCellStyle="Millares 3">
   <autoFilter ref="A1:L2" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="distribuidora" dataDxfId="139" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="nro_partida" dataDxfId="138" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="descripcion_partida" dataDxfId="137" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="tipo_gasto" dataDxfId="136" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="grupo_gasto" dataDxfId="135" dataCellStyle="Millares"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="asignacion_inicial" dataDxfId="134" dataCellStyle="Millares 3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="reformas" dataDxfId="133" dataCellStyle="Millares 3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="presupuesto_codificado" dataDxfId="132" dataCellStyle="Millares 3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="pre_compromiso" dataDxfId="131" dataCellStyle="Millares 3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="compromiso" dataDxfId="130" dataCellStyle="Millares 3"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="devengado" dataDxfId="129" dataCellStyle="Millares 3"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="pagado" dataDxfId="128" dataCellStyle="Millares 3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="distribuidora" dataDxfId="141" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="nro_partida" dataDxfId="140" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="descripcion_partida" dataDxfId="139" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="tipo_gasto" dataDxfId="138" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="grupo_gasto" dataDxfId="137" dataCellStyle="Millares"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="asignacion_inicial" dataDxfId="136" dataCellStyle="Millares 3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="reformas" dataDxfId="135" dataCellStyle="Millares 3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="presupuesto_codificado" dataDxfId="134" dataCellStyle="Millares 3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="pre_compromiso" dataDxfId="133" dataCellStyle="Millares 3"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="compromiso" dataDxfId="132" dataCellStyle="Millares 3"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="devengado" dataDxfId="131" dataCellStyle="Millares 3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="pagado" dataDxfId="130" dataCellStyle="Millares 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12072,140 +12095,146 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Anualidad_SAPG" displayName="Anualidad_SAPG" ref="A1:AR2" totalsRowShown="0" headerRowDxfId="127" dataDxfId="125" headerRowBorderDxfId="126" tableBorderDxfId="124" totalsRowBorderDxfId="123" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Anualidad_SAPG" displayName="Anualidad_SAPG" ref="A1:AR2" totalsRowShown="0" headerRowDxfId="129" dataDxfId="127" headerRowBorderDxfId="128" tableBorderDxfId="126" totalsRowBorderDxfId="125" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
   <autoFilter ref="A1:AR2" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="44">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="distribuidora" dataDxfId="122" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="proyecto_arrastre" dataDxfId="121" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="proyecto_calificado_ecostos" dataDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="anio_calificacion" dataDxfId="119"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="codigo_ecostos" dataDxfId="118"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0400-00002C000000}" name="rubro_arrastre" dataDxfId="117"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="codigo_proyecto_eed" dataDxfId="116"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="nombre_proyecto" dataDxfId="115"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="objeto_proyecto" dataDxfId="114"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="provincia" dataDxfId="113"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="canton" dataDxfId="112"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="parroquia" dataDxfId="111"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="estado_proyecto" dataDxfId="110"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="etapa_ejecucion_proyecto" dataDxfId="109"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="avance_ejecucion_fisica" dataDxfId="108" dataCellStyle="Porcentaje 2"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="avance_ejecucion_total" dataDxfId="107"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="fecha_inicio_proyecto" dataDxfId="106" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="fecha_pro_fin_proyecto" dataDxfId="105" dataCellStyle="Millares 3"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="fecha_fin_proyecto" dataDxfId="104" dataCellStyle="Millares 3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="monto_calificado" dataDxfId="103" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="presupuesto_codificado_arrastre" dataDxfId="102" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" name="devengado_arrastre" dataDxfId="101" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="pagado_arrastre" dataDxfId="100" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="asignacion_inicial" dataDxfId="99" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" name="reformas" dataDxfId="98" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="presupuesto_codificado" dataDxfId="97" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0400-00001A000000}" name="pre_compromiso" dataDxfId="96" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0400-00001B000000}" name="compromiso" dataDxfId="95" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0400-00001C000000}" name="devengado" dataDxfId="94" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0400-00001D000000}" name="pagado" dataDxfId="93" dataCellStyle="Millares"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0400-00001E000000}" name="anticipo_no_amortizado" dataDxfId="92" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0400-00001F000000}" name="Ln_inst_tipo" dataDxfId="91" dataCellStyle="Millares 3"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0400-000020000000}" name="Ln_inst_potencia" dataDxfId="90" dataCellStyle="Millares 3"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0400-000021000000}" name="Ln_inst_cantidad" dataDxfId="89" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0400-000022000000}" name="Ln_reemp_tipo" dataDxfId="88" dataCellStyle="Millares 3"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0400-000023000000}" name="Ln_reemp_potencia" dataDxfId="87" dataCellStyle="Millares 3"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0400-000024000000}" name="Ln_reemp_cantidad" dataDxfId="86" dataCellStyle="Millares 3"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0400-000025000000}" name="Lumin_inst_total" dataDxfId="85" dataCellStyle="Millares 3"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0400-000026000000}" name="Postes_nuev_número" dataDxfId="84" dataCellStyle="Millares 3"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0400-000027000000}" name="Postes_reemp_número" dataDxfId="83" dataCellStyle="Millares 3"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0400-000028000000}" name="Benef_dir_número" dataDxfId="82" dataCellStyle="Millares 3"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0400-000029000000}" name="empleos_generados" dataDxfId="81" dataCellStyle="Millares 3"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0400-00002E000000}" name="nro_personal_fem" dataDxfId="80" dataCellStyle="Millares 3"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0400-00002A000000}" name="observaciones" dataDxfId="79" dataCellStyle="Millares 3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="distribuidora" dataDxfId="124" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="proyecto_arrastre" dataDxfId="123" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="proyecto_calificado_ecostos" dataDxfId="122"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="anio_calificacion" dataDxfId="121"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="codigo_ecostos" dataDxfId="120"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0400-00002C000000}" name="rubro_arrastre" dataDxfId="119"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="codigo_proyecto_eed" dataDxfId="118"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="nombre_proyecto" dataDxfId="117"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="objeto_proyecto" dataDxfId="116"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="provincia" dataDxfId="115"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="canton" dataDxfId="114"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="parroquia" dataDxfId="113"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="estado_proyecto" dataDxfId="112"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="etapa_ejecucion_proyecto" dataDxfId="111"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="avance_ejecucion_fisica" dataDxfId="110" dataCellStyle="Porcentaje 2"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="avance_ejecucion_total" dataDxfId="3" dataCellStyle="Porcentaje 2">
+      <calculatedColumnFormula>+IF($N2="No iniciado 0%",0%,IF($O2="Elaboración de pliegos 5%",5%,IF($N2="Disponibilidad de pliegos 10%",10%,IF($N2="Publicación del proceso 15%",15%,IF($N2="Resolución de adjudicación 30%",30%,IF($N2="Adjudicación y firma de contrato 40%",40%,IF($N2="En ejecución 41% - 90%",(40%+($O2*50%)),IF($N2="Acta de entrega - recepción 95%",IF($O2=100%,95%,""),IF($N2="Registro contable 100%",IF($O2=100%,100%,""),"")))))))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="fecha_inicio_proyecto" dataDxfId="109" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="fecha_pro_fin_proyecto" dataDxfId="108" dataCellStyle="Millares 3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="fecha_fin_proyecto" dataDxfId="107" dataCellStyle="Millares 3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="monto_calificado" dataDxfId="106" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="presupuesto_codificado_arrastre" dataDxfId="105" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" name="devengado_arrastre" dataDxfId="104" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="pagado_arrastre" dataDxfId="103" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="asignacion_inicial" dataDxfId="102" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" name="reformas" dataDxfId="101" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="presupuesto_codificado" dataDxfId="100" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0400-00001A000000}" name="pre_compromiso" dataDxfId="99" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0400-00001B000000}" name="compromiso" dataDxfId="98" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0400-00001C000000}" name="devengado" dataDxfId="97" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0400-00001D000000}" name="pagado" dataDxfId="96" dataCellStyle="Millares"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0400-00001E000000}" name="anticipo_no_amortizado" dataDxfId="95" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0400-00001F000000}" name="Ln_inst_tipo" dataDxfId="94" dataCellStyle="Millares 3"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0400-000020000000}" name="Ln_inst_potencia" dataDxfId="93" dataCellStyle="Millares 3"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0400-000021000000}" name="Ln_inst_cantidad" dataDxfId="92" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0400-000022000000}" name="Ln_reemp_tipo" dataDxfId="91" dataCellStyle="Millares 3"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0400-000023000000}" name="Ln_reemp_potencia" dataDxfId="90" dataCellStyle="Millares 3"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0400-000024000000}" name="Ln_reemp_cantidad" dataDxfId="89" dataCellStyle="Millares 3"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0400-000025000000}" name="Lumin_inst_total" dataDxfId="88" dataCellStyle="Millares 3"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0400-000026000000}" name="Postes_nuev_número" dataDxfId="87" dataCellStyle="Millares 3"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0400-000027000000}" name="Postes_reemp_número" dataDxfId="86" dataCellStyle="Millares 3"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0400-000028000000}" name="Benef_dir_número" dataDxfId="85" dataCellStyle="Millares 3"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0400-000029000000}" name="empleos_generados" dataDxfId="84" dataCellStyle="Millares 3"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0400-00002E000000}" name="nro_personal_fem" dataDxfId="83" dataCellStyle="Millares 3"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0400-00002A000000}" name="observaciones" dataDxfId="82" dataCellStyle="Millares 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Expansión_SAPG" displayName="Expansión_SAPG" ref="A1:AN2" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Expansión_SAPG" displayName="Expansión_SAPG" ref="A1:AN2" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78" totalsRowBorderDxfId="77" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
   <autoFilter ref="A1:AN2" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="distribuidora" dataDxfId="73" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="proyecto_arrastre" dataDxfId="72" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="anio_calificacion" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="codigo_proyecto_eed" dataDxfId="70"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="nombre_proyecto" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="objeto_proyecto" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="provincia" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="canton" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="parroquia" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="estado_proyecto" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="etapa_ejecucion_proyecto" dataDxfId="63"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="avance_ejecucion_fisica" dataDxfId="62" dataCellStyle="Porcentaje 2"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="avance_ejecucion_total" dataDxfId="61"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0500-000010000000}" name="fecha_inicio_proyecto" dataDxfId="60" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0500-000011000000}" name="fecha_pro_fin_proyecto" dataDxfId="59" dataCellStyle="Millares 3"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="fecha_fin_proyecto" dataDxfId="58"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0500-000014000000}" name="presupuesto_codificado_arrastre" dataDxfId="57" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0500-000015000000}" name="devengado_arrastre" dataDxfId="56" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0500-000016000000}" name="pagado_arrastre" dataDxfId="55" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0500-000017000000}" name="asignacion_inicial" dataDxfId="54" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0500-000018000000}" name="reformas" dataDxfId="53" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0500-000019000000}" name="presupuesto_codificado" dataDxfId="52" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0500-00001A000000}" name="pre_compromiso" dataDxfId="51" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0500-00001B000000}" name="compromiso" dataDxfId="50" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0500-00001C000000}" name="devengado" dataDxfId="49" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0500-00001D000000}" name="pagado" dataDxfId="48" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0500-00001E000000}" name="anticipo_no_amortizado" dataDxfId="47" dataCellStyle="Moneda"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0500-00001F000000}" name="Ln_inst_tipo" dataDxfId="46" dataCellStyle="Millares 3"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0500-000020000000}" name="Ln_inst_potencia" dataDxfId="45" dataCellStyle="Millares 3"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0500-000021000000}" name="Ln_inst_cantidad" dataDxfId="44" dataCellStyle="Millares 3"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0500-000022000000}" name="Ln_reemp_tipo" dataDxfId="43" dataCellStyle="Millares 3"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0500-000023000000}" name="Ln_reemp_potencia" dataDxfId="42" dataCellStyle="Millares 3"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0500-000024000000}" name="Ln_reemp_cantidad" dataDxfId="41" dataCellStyle="Millares 3"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0500-000025000000}" name="Lumin_inst_total" dataDxfId="40" dataCellStyle="Millares 3"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0500-000026000000}" name="Postes_nuev_número" dataDxfId="39" dataCellStyle="Millares 3"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0500-000027000000}" name="Postes_reemp_número" dataDxfId="38" dataCellStyle="Millares 3"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0500-000028000000}" name="Benef_dir_número" dataDxfId="37" dataCellStyle="Millares 3"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0500-000029000000}" name="empleos_generados" dataDxfId="36" dataCellStyle="Millares 3"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0500-00002C000000}" name="nro_personal_fem" dataDxfId="35" dataCellStyle="Millares 3"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0500-00002A000000}" name="observaciones" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="distribuidora" dataDxfId="76" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="proyecto_arrastre" dataDxfId="75" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="anio_calificacion" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="codigo_proyecto_eed" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="nombre_proyecto" dataDxfId="72"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="objeto_proyecto" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="provincia" dataDxfId="70"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="canton" dataDxfId="69"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="parroquia" dataDxfId="68"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="estado_proyecto" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="etapa_ejecucion_proyecto" dataDxfId="66"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="avance_ejecucion_fisica" dataDxfId="65" dataCellStyle="Porcentaje 2"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="avance_ejecucion_total" dataDxfId="2">
+      <calculatedColumnFormula>+IF($K2="No iniciado 0%",0%,IF($K2="Elaboración de pliegos 5%",5%,IF($K2="Disponibilidad de pliegos 10%",10%,IF($K2="Publicación del proceso 15%",15%,IF($K2="Resolución de adjudicación 30%",30%,IF($K2="Adjudicación y firma de contrato 40%",40%,IF($K2="En ejecución 41% - 90%",(40%+($L2*50%)),IF($K2="Acta de entrega - recepción 95%",IF($L2=100%,95%,""),IF($K2="Registro contable 100%",IF($L2=100%,100%,""),"")))))))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0500-000010000000}" name="fecha_inicio_proyecto" dataDxfId="64" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0500-000011000000}" name="fecha_pro_fin_proyecto" dataDxfId="63" dataCellStyle="Millares 3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="fecha_fin_proyecto" dataDxfId="62"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0500-000014000000}" name="presupuesto_codificado_arrastre" dataDxfId="61" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0500-000015000000}" name="devengado_arrastre" dataDxfId="60" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0500-000016000000}" name="pagado_arrastre" dataDxfId="59" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0500-000017000000}" name="asignacion_inicial" dataDxfId="58" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0500-000018000000}" name="reformas" dataDxfId="57" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0500-000019000000}" name="presupuesto_codificado" dataDxfId="56" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0500-00001A000000}" name="pre_compromiso" dataDxfId="55" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0500-00001B000000}" name="compromiso" dataDxfId="54" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0500-00001C000000}" name="devengado" dataDxfId="53" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0500-00001D000000}" name="pagado" dataDxfId="52" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0500-00001E000000}" name="anticipo_no_amortizado" dataDxfId="51" dataCellStyle="Moneda"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0500-00001F000000}" name="Ln_inst_tipo" dataDxfId="50" dataCellStyle="Millares 3"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0500-000020000000}" name="Ln_inst_potencia" dataDxfId="49" dataCellStyle="Millares 3"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0500-000021000000}" name="Ln_inst_cantidad" dataDxfId="48" dataCellStyle="Millares 3"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0500-000022000000}" name="Ln_reemp_tipo" dataDxfId="47" dataCellStyle="Millares 3"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0500-000023000000}" name="Ln_reemp_potencia" dataDxfId="46" dataCellStyle="Millares 3"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0500-000024000000}" name="Ln_reemp_cantidad" dataDxfId="45" dataCellStyle="Millares 3"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0500-000025000000}" name="Lumin_inst_total" dataDxfId="44" dataCellStyle="Millares 3"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0500-000026000000}" name="Postes_nuev_número" dataDxfId="43" dataCellStyle="Millares 3"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0500-000027000000}" name="Postes_reemp_número" dataDxfId="42" dataCellStyle="Millares 3"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0500-000028000000}" name="Benef_dir_número" dataDxfId="41" dataCellStyle="Millares 3"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0500-000029000000}" name="empleos_generados" dataDxfId="40" dataCellStyle="Millares 3"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0500-00002C000000}" name="nro_personal_fem" dataDxfId="39" dataCellStyle="Millares 3"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0500-00002A000000}" name="observaciones" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F6B13584-90B9-40C6-859F-42085C6D849D}" name="Expansión_SAPG14" displayName="Expansión_SAPG14" ref="A1:AC2" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F6B13584-90B9-40C6-859F-42085C6D849D}" name="Expansión_SAPG14" displayName="Expansión_SAPG14" ref="A1:AC2" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33" headerRowCellStyle="Normal 2" dataCellStyle="Millares 3">
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{4079842F-5FDE-4980-976B-51FA04B22345}" name="distribuidora" dataDxfId="28" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="4" xr3:uid="{71EDF401-E6D2-43C6-BCA6-AD205BCC077E}" name="fuente" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{C5B0F89F-09A6-44A7-AA07-5F6256AE1DC5}" name="proyecto_arrastre" dataDxfId="26" dataCellStyle="Normal_Hoja1"/>
-    <tableColumn id="3" xr3:uid="{9AB0F8BC-025D-4574-A017-DB0B270526E9}" name="servicio" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{D1A9FA6C-C4BB-444B-A7A1-F4527D2F9DD4}" name="codigo_proyecto_eed" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{64E54765-5314-4CAD-A63B-9E383C3A9573}" name="nombre_proyecto" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{3C38D244-2998-45DB-8291-5630D39C4773}" name="objeto_proyecto" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{A6141303-5C3D-48B9-9966-55EFE2739FBE}" name="provincia" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{08C68E93-AFA7-4B73-9B58-8F85B3B6544D}" name="canton" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{97760BF4-C45B-4C8F-835F-1EDB85833147}" name="parroquia" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{D7145B13-BBAF-4645-9E9B-4FAB719B5F2C}" name="estado_proyecto" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{7B6351B2-F92E-43A3-AD3E-A29159CDA4AD}" name="etapa_ejecucion_proyecto" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{58CA3E44-F725-486B-8315-8BCA3F43DA55}" name="avance_ejecucion_fisica" dataDxfId="16" dataCellStyle="Porcentaje 2"/>
-    <tableColumn id="15" xr3:uid="{4C42F86A-1994-41C2-9EA9-AD9345A0B24B}" name="avance_ejecucion_total" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{D17192EF-2441-48DD-BCBF-E356D434F366}" name="fecha_inicio_proyecto" dataDxfId="14" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{85D8B59D-8053-4403-8BB2-4D608A8ABD8A}" name="fecha_pro_fin_proyecto" dataDxfId="13" dataCellStyle="Millares 3"/>
-    <tableColumn id="18" xr3:uid="{60CC09A3-5031-454C-B5EE-FDD8DD70B39A}" name="fecha_fin_proyecto" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{12679A4D-E41A-4D2B-9ED3-05CBF3DAE896}" name="presupuesto_codificado_arrastre" dataDxfId="11" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{2978E973-4BE9-4B59-8E90-A8EFD5922384}" name="devengado_arrastre" dataDxfId="10" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{8104F45F-E928-4E8C-B83A-842B38500680}" name="pagado_arrastre" dataDxfId="9" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{6EC1AE4A-1776-4987-86CC-439FA4876906}" name="asignacion_inicial" dataDxfId="8" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{42BFC224-D2DD-40B2-9067-58B83FE49EA1}" name="reformas" dataDxfId="7" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{104BD540-486D-4D99-9622-60FD17BEAF70}" name="presupuesto_codificado" dataDxfId="6" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{D99C28F0-A1C6-485E-8A6B-CFB44412EABF}" name="pre_compromiso" dataDxfId="5" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{B1120E28-9DF2-413D-A003-A53B7C85D582}" name="compromiso" dataDxfId="4" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{EFB79F8D-05B2-4257-B0D9-D2CE3801A8CD}" name="devengado" dataDxfId="3" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{50834D0C-CE4E-4FA4-B01D-7888717AC543}" name="pagado" dataDxfId="2" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{8AD03585-74D1-4BB7-9BC7-CBF9DF979C1E}" name="anticipo_no_amortizado" dataDxfId="1" dataCellStyle="Moneda"/>
-    <tableColumn id="42" xr3:uid="{539D98EF-E85A-4150-8939-4797D08B39D9}" name="observaciones" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{4079842F-5FDE-4980-976B-51FA04B22345}" name="distribuidora" dataDxfId="32" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="4" xr3:uid="{71EDF401-E6D2-43C6-BCA6-AD205BCC077E}" name="fuente" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{C5B0F89F-09A6-44A7-AA07-5F6256AE1DC5}" name="proyecto_arrastre" dataDxfId="30" dataCellStyle="Normal_Hoja1"/>
+    <tableColumn id="3" xr3:uid="{9AB0F8BC-025D-4574-A017-DB0B270526E9}" name="servicio" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{D1A9FA6C-C4BB-444B-A7A1-F4527D2F9DD4}" name="codigo_proyecto_eed" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{64E54765-5314-4CAD-A63B-9E383C3A9573}" name="nombre_proyecto" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{3C38D244-2998-45DB-8291-5630D39C4773}" name="objeto_proyecto" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{A6141303-5C3D-48B9-9966-55EFE2739FBE}" name="provincia" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{08C68E93-AFA7-4B73-9B58-8F85B3B6544D}" name="canton" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{97760BF4-C45B-4C8F-835F-1EDB85833147}" name="parroquia" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{D7145B13-BBAF-4645-9E9B-4FAB719B5F2C}" name="estado_proyecto" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{7B6351B2-F92E-43A3-AD3E-A29159CDA4AD}" name="etapa_ejecucion_proyecto" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{58CA3E44-F725-486B-8315-8BCA3F43DA55}" name="avance_ejecucion_fisica" dataDxfId="20" dataCellStyle="Porcentaje 2"/>
+    <tableColumn id="15" xr3:uid="{4C42F86A-1994-41C2-9EA9-AD9345A0B24B}" name="avance_ejecucion_total" dataDxfId="1">
+      <calculatedColumnFormula>+IF($L2="No iniciado 0%",0%,IF($L2="Elaboración de pliegos 5%",5%,IF($L2="Disponibilidad de pliegos 10%",10%,IF($L2="Publicación del proceso 15%",15%,IF($L2="Resolución de adjudicación 30%",30%,IF($L2="Adjudicación y firma de contrato 40%",40%,IF($L2="En ejecución 41% - 90%",(40%+($M2*50%)),IF($L2="Acta de entrega - recepción 95%",IF($M2=100%,95%,""),IF($L2="Registro contable 100%",IF($M2=100%,100%,""),"")))))))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{D17192EF-2441-48DD-BCBF-E356D434F366}" name="fecha_inicio_proyecto" dataDxfId="19" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{85D8B59D-8053-4403-8BB2-4D608A8ABD8A}" name="fecha_pro_fin_proyecto" dataDxfId="18" dataCellStyle="Millares 3"/>
+    <tableColumn id="18" xr3:uid="{60CC09A3-5031-454C-B5EE-FDD8DD70B39A}" name="fecha_fin_proyecto" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{12679A4D-E41A-4D2B-9ED3-05CBF3DAE896}" name="presupuesto_codificado_arrastre" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{2978E973-4BE9-4B59-8E90-A8EFD5922384}" name="devengado_arrastre" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{8104F45F-E928-4E8C-B83A-842B38500680}" name="pagado_arrastre" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{6EC1AE4A-1776-4987-86CC-439FA4876906}" name="asignacion_inicial" dataDxfId="13" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{42BFC224-D2DD-40B2-9067-58B83FE49EA1}" name="reformas" dataDxfId="12" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{104BD540-486D-4D99-9622-60FD17BEAF70}" name="presupuesto_codificado" dataDxfId="11" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{D99C28F0-A1C6-485E-8A6B-CFB44412EABF}" name="pre_compromiso" dataDxfId="10" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{B1120E28-9DF2-413D-A003-A53B7C85D582}" name="compromiso" dataDxfId="9" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{EFB79F8D-05B2-4257-B0D9-D2CE3801A8CD}" name="devengado" dataDxfId="8" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{50834D0C-CE4E-4FA4-B01D-7888717AC543}" name="pagado" dataDxfId="7" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{8AD03585-74D1-4BB7-9BC7-CBF9DF979C1E}" name="anticipo_no_amortizado" dataDxfId="6" dataCellStyle="Moneda"/>
+    <tableColumn id="42" xr3:uid="{539D98EF-E85A-4150-8939-4797D08B39D9}" name="observaciones" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13257,7 +13286,10 @@
       <c r="M2" s="193"/>
       <c r="N2" s="194"/>
       <c r="O2" s="187"/>
-      <c r="P2" s="152"/>
+      <c r="P2" s="196" t="str">
+        <f>+IF($N2="No iniciado 0%",0%,IF($O2="Elaboración de pliegos 5%",5%,IF($N2="Disponibilidad de pliegos 10%",10%,IF($N2="Publicación del proceso 15%",15%,IF($N2="Resolución de adjudicación 30%",30%,IF($N2="Adjudicación y firma de contrato 40%",40%,IF($N2="En ejecución 41% - 90%",(40%+($O2*50%)),IF($N2="Acta de entrega - recepción 95%",IF($O2=100%,95%,""),IF($N2="Registro contable 100%",IF($O2=100%,100%,""),"")))))))))</f>
+        <v/>
+      </c>
       <c r="Q2" s="188"/>
       <c r="R2" s="188"/>
       <c r="S2" s="188"/>
@@ -13490,7 +13522,10 @@
       <c r="J2" s="169"/>
       <c r="K2" s="149"/>
       <c r="L2" s="198"/>
-      <c r="M2" s="152"/>
+      <c r="M2" s="152" t="str">
+        <f>+IF($K2="No iniciado 0%",0%,IF($K2="Elaboración de pliegos 5%",5%,IF($K2="Disponibilidad de pliegos 10%",10%,IF($K2="Publicación del proceso 15%",15%,IF($K2="Resolución de adjudicación 30%",30%,IF($K2="Adjudicación y firma de contrato 40%",40%,IF($K2="En ejecución 41% - 90%",(40%+($L2*50%)),IF($K2="Acta de entrega - recepción 95%",IF($L2=100%,95%,""),IF($K2="Registro contable 100%",IF($L2=100%,100%,""),"")))))))))</f>
+        <v/>
+      </c>
       <c r="N2" s="188"/>
       <c r="O2" s="188"/>
       <c r="P2" s="149"/>
@@ -13524,7 +13559,7 @@
   <sheetProtection selectLockedCells="1"/>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="5">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="L2:M2 Q2:AA2" xr:uid="{00000000-0002-0000-0F00-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="Q2:AA2 L2:M2" xr:uid="{00000000-0002-0000-0F00-000000000000}">
       <formula1>ISNUMBER(L2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0F00-000001000000}">
@@ -13679,7 +13714,10 @@
       <c r="K2" s="169"/>
       <c r="L2" s="149"/>
       <c r="M2" s="198"/>
-      <c r="N2" s="152"/>
+      <c r="N2" s="152" t="str">
+        <f>+IF($L2="No iniciado 0%",0%,IF($L2="Elaboración de pliegos 5%",5%,IF($L2="Disponibilidad de pliegos 10%",10%,IF($L2="Publicación del proceso 15%",15%,IF($L2="Resolución de adjudicación 30%",30%,IF($L2="Adjudicación y firma de contrato 40%",40%,IF($L2="En ejecución 41% - 90%",(40%+($M2*50%)),IF($L2="Acta de entrega - recepción 95%",IF($M2=100%,95%,""),IF($L2="Registro contable 100%",IF($M2=100%,100%,""),"")))))))))</f>
+        <v/>
+      </c>
       <c r="O2" s="188"/>
       <c r="P2" s="188"/>
       <c r="Q2" s="149"/>
@@ -13706,7 +13744,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{533A1528-A7C2-4BF9-AF60-A07E72952C55}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="M2:N2 R2:AB2" xr:uid="{7F0D7675-3345-4282-905D-DCD1EAECBD8A}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="R2:AB2 M2:N2" xr:uid="{7F0D7675-3345-4282-905D-DCD1EAECBD8A}">
       <formula1>ISNUMBER(M2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos de tipo texto" sqref="B2" xr:uid="{0AA238A3-4ABA-4A31-83F4-4FD50039AB32}">
@@ -25789,11 +25827,11 @@
     </row>
     <row r="11" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="85"/>
-      <c r="B11" s="250" t="s">
+      <c r="B11" s="256" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="250"/>
-      <c r="D11" s="250"/>
+      <c r="C11" s="256"/>
+      <c r="D11" s="256"/>
       <c r="E11" s="79" t="s">
         <v>29</v>
       </c>
@@ -25819,28 +25857,28 @@
     </row>
     <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="85"/>
-      <c r="B12" s="251" t="s">
+      <c r="B12" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="251"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="257" t="s">
+      <c r="C12" s="264"/>
+      <c r="D12" s="264"/>
+      <c r="E12" s="249" t="s">
         <v>345</v>
       </c>
-      <c r="F12" s="258"/>
-      <c r="G12" s="258"/>
-      <c r="H12" s="258"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="258"/>
-      <c r="K12" s="259"/>
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="250"/>
+      <c r="J12" s="250"/>
+      <c r="K12" s="251"/>
       <c r="L12" s="85"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="265" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="252"/>
-      <c r="D13" s="252"/>
+      <c r="C13" s="265"/>
+      <c r="D13" s="265"/>
       <c r="E13" s="231">
         <v>0</v>
       </c>
@@ -25865,12 +25903,12 @@
       <c r="L13" s="85"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="252" t="str">
+      <c r="B14" s="265" t="str">
         <f>+'FORM INGRESOS'!A17</f>
         <v>Déficit Tarifario</v>
       </c>
-      <c r="C14" s="252"/>
-      <c r="D14" s="252"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="265"/>
       <c r="E14" s="232">
         <v>0</v>
       </c>
@@ -25895,12 +25933,12 @@
       <c r="L14" s="85"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="252" t="str">
+      <c r="B15" s="265" t="str">
         <f>+'FORM INGRESOS'!A19</f>
         <v>Subsidios (Informativo)</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="D15" s="252"/>
+      <c r="C15" s="265"/>
+      <c r="D15" s="265"/>
       <c r="E15" s="232">
         <v>0</v>
       </c>
@@ -25925,12 +25963,12 @@
       <c r="L15" s="85"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="252" t="str">
+      <c r="B16" s="265" t="str">
         <f>+'FORM INGRESOS'!A18</f>
         <v>Intereses Ganados</v>
       </c>
-      <c r="C16" s="252"/>
-      <c r="D16" s="252"/>
+      <c r="C16" s="265"/>
+      <c r="D16" s="265"/>
       <c r="E16" s="232">
         <v>0</v>
       </c>
@@ -25955,12 +25993,12 @@
       <c r="L16" s="85"/>
     </row>
     <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="252" t="str">
+      <c r="B17" s="265" t="str">
         <f>+'FORM INGRESOS'!A20</f>
         <v>OTROS INGRESOS NO OPERATIVOS</v>
       </c>
-      <c r="C17" s="252"/>
-      <c r="D17" s="252"/>
+      <c r="C17" s="265"/>
+      <c r="D17" s="265"/>
       <c r="E17" s="232">
         <v>0</v>
       </c>
@@ -25985,11 +26023,11 @@
       <c r="L17" s="85"/>
     </row>
     <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="253" t="s">
+      <c r="B18" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="253"/>
-      <c r="D18" s="253"/>
+      <c r="C18" s="262"/>
+      <c r="D18" s="262"/>
       <c r="E18" s="230">
         <f>+E13-E14-E15+E16+E17</f>
         <v>0</v>
@@ -26021,11 +26059,11 @@
       <c r="L18" s="85"/>
     </row>
     <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="252" t="s">
+      <c r="B19" s="265" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="252"/>
-      <c r="D19" s="252"/>
+      <c r="C19" s="265"/>
+      <c r="D19" s="265"/>
       <c r="E19" s="231"/>
       <c r="F19" s="231"/>
       <c r="G19" s="231"/>
@@ -26036,11 +26074,11 @@
       <c r="L19" s="85"/>
     </row>
     <row r="20" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="254"/>
-      <c r="D20" s="254"/>
+      <c r="C20" s="261"/>
+      <c r="D20" s="261"/>
       <c r="E20" s="231"/>
       <c r="F20" s="231"/>
       <c r="G20" s="231"/>
@@ -26109,11 +26147,11 @@
       <c r="L22" s="85"/>
     </row>
     <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="249" t="s">
+      <c r="B23" s="257" t="s">
         <v>143</v>
       </c>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
+      <c r="C23" s="257"/>
+      <c r="D23" s="257"/>
       <c r="E23" s="232">
         <v>0</v>
       </c>
@@ -26138,11 +26176,11 @@
       <c r="L23" s="85"/>
     </row>
     <row r="24" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="254" t="s">
+      <c r="B24" s="261" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="254"/>
-      <c r="D24" s="254"/>
+      <c r="C24" s="261"/>
+      <c r="D24" s="261"/>
       <c r="E24" s="232"/>
       <c r="F24" s="232"/>
       <c r="G24" s="232"/>
@@ -26182,11 +26220,11 @@
       <c r="L25" s="85"/>
     </row>
     <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="249" t="s">
+      <c r="B26" s="257" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="249"/>
-      <c r="D26" s="249"/>
+      <c r="C26" s="257"/>
+      <c r="D26" s="257"/>
       <c r="E26" s="232">
         <v>0</v>
       </c>
@@ -26211,9 +26249,9 @@
       <c r="L26" s="85"/>
     </row>
     <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="249"/>
-      <c r="C27" s="249"/>
-      <c r="D27" s="249"/>
+      <c r="B27" s="257"/>
+      <c r="C27" s="257"/>
+      <c r="D27" s="257"/>
       <c r="E27" s="232"/>
       <c r="F27" s="232"/>
       <c r="G27" s="232"/>
@@ -26224,11 +26262,11 @@
       <c r="L27" s="85"/>
     </row>
     <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="249" t="s">
+      <c r="B28" s="257" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
+      <c r="C28" s="257"/>
+      <c r="D28" s="257"/>
       <c r="E28" s="232">
         <v>0</v>
       </c>
@@ -26253,11 +26291,11 @@
       <c r="L28" s="85"/>
     </row>
     <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="257" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="D29" s="249"/>
+      <c r="C29" s="257"/>
+      <c r="D29" s="257"/>
       <c r="E29" s="232">
         <v>0</v>
       </c>
@@ -26282,11 +26320,11 @@
       <c r="L29" s="85"/>
     </row>
     <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="253" t="s">
+      <c r="B30" s="262" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="253"/>
-      <c r="D30" s="253"/>
+      <c r="C30" s="262"/>
+      <c r="D30" s="262"/>
       <c r="E30" s="230">
         <f>SUM(E19:E29)</f>
         <v>0</v>
@@ -26318,11 +26356,11 @@
       <c r="L30" s="85"/>
     </row>
     <row r="31" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="256" t="s">
+      <c r="B31" s="263" t="s">
         <v>149</v>
       </c>
-      <c r="C31" s="256"/>
-      <c r="D31" s="256"/>
+      <c r="C31" s="263"/>
+      <c r="D31" s="263"/>
       <c r="E31" s="230">
         <f>+E18-E30</f>
         <v>0</v>
@@ -26354,11 +26392,11 @@
       <c r="L31" s="85"/>
     </row>
     <row r="32" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="251" t="s">
+      <c r="B32" s="264" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="251"/>
-      <c r="D32" s="251"/>
+      <c r="C32" s="264"/>
+      <c r="D32" s="264"/>
       <c r="E32" s="210"/>
       <c r="F32" s="210"/>
       <c r="G32" s="210"/>
@@ -26369,11 +26407,11 @@
       <c r="L32" s="85"/>
     </row>
     <row r="33" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="254" t="s">
+      <c r="B33" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="254"/>
-      <c r="D33" s="254"/>
+      <c r="C33" s="261"/>
+      <c r="D33" s="261"/>
       <c r="E33" s="211"/>
       <c r="F33" s="211"/>
       <c r="G33" s="211"/>
@@ -26442,9 +26480,9 @@
       <c r="L35" s="85"/>
     </row>
     <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="263"/>
-      <c r="C36" s="264"/>
-      <c r="D36" s="265"/>
+      <c r="B36" s="258"/>
+      <c r="C36" s="259"/>
+      <c r="D36" s="260"/>
       <c r="E36" s="232"/>
       <c r="F36" s="232"/>
       <c r="G36" s="232"/>
@@ -26455,11 +26493,11 @@
       <c r="L36" s="85"/>
     </row>
     <row r="37" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="261" t="s">
         <v>144</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="D37" s="254"/>
+      <c r="C37" s="261"/>
+      <c r="D37" s="261"/>
       <c r="E37" s="232"/>
       <c r="F37" s="232"/>
       <c r="G37" s="232"/>
@@ -26528,11 +26566,11 @@
       <c r="L39" s="85"/>
     </row>
     <row r="40" spans="2:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
+      <c r="B40" s="253" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="262"/>
+      <c r="C40" s="254"/>
+      <c r="D40" s="254"/>
       <c r="E40" s="232"/>
       <c r="F40" s="232"/>
       <c r="G40" s="232"/>
@@ -26543,7 +26581,7 @@
       <c r="L40" s="85"/>
     </row>
     <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="249" t="s">
+      <c r="B41" s="257" t="s">
         <v>152</v>
       </c>
       <c r="C41" s="255"/>
@@ -26572,7 +26610,7 @@
       <c r="L41" s="85"/>
     </row>
     <row r="42" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="249" t="s">
+      <c r="B42" s="257" t="s">
         <v>153</v>
       </c>
       <c r="C42" s="255"/>
@@ -26601,7 +26639,7 @@
       <c r="L42" s="85"/>
     </row>
     <row r="43" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="249"/>
+      <c r="B43" s="257"/>
       <c r="C43" s="255"/>
       <c r="D43" s="255"/>
       <c r="E43" s="232"/>
@@ -26614,11 +26652,11 @@
       <c r="L43" s="85"/>
     </row>
     <row r="44" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="261" t="s">
+      <c r="B44" s="253" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="262"/>
-      <c r="D44" s="262"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
       <c r="E44" s="232"/>
       <c r="F44" s="232"/>
       <c r="G44" s="232"/>
@@ -26716,11 +26754,11 @@
       <c r="L47" s="85"/>
     </row>
     <row r="48" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="250" t="s">
+      <c r="B48" s="256" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="250"/>
-      <c r="D48" s="250"/>
+      <c r="C48" s="256"/>
+      <c r="D48" s="256"/>
       <c r="E48" s="230">
         <f>SUM(E33:E47)</f>
         <v>0</v>
@@ -26765,18 +26803,18 @@
       <c r="L49" s="87"/>
     </row>
     <row r="50" spans="1:30" s="83" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="260" t="s">
+      <c r="B50" s="252" t="s">
         <v>275</v>
       </c>
-      <c r="C50" s="260"/>
-      <c r="D50" s="260"/>
-      <c r="E50" s="260"/>
-      <c r="F50" s="260"/>
-      <c r="G50" s="260"/>
-      <c r="H50" s="260"/>
-      <c r="I50" s="260"/>
-      <c r="J50" s="260"/>
-      <c r="K50" s="260"/>
+      <c r="C50" s="252"/>
+      <c r="D50" s="252"/>
+      <c r="E50" s="252"/>
+      <c r="F50" s="252"/>
+      <c r="G50" s="252"/>
+      <c r="H50" s="252"/>
+      <c r="I50" s="252"/>
+      <c r="J50" s="252"/>
+      <c r="K50" s="252"/>
       <c r="L50" s="88"/>
       <c r="M50" s="84"/>
       <c r="N50" s="84"/>
@@ -26816,6 +26854,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="E12:K12"/>
     <mergeCell ref="B50:K50"/>
     <mergeCell ref="B44:D44"/>
@@ -26832,30 +26894,6 @@
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -27585,14 +27623,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="138" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="256" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250" t="s">
+      <c r="B1" s="256"/>
+      <c r="C1" s="256" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="250"/>
+      <c r="D1" s="256"/>
       <c r="E1" s="79" t="s">
         <v>320</v>
       </c>
@@ -27620,14 +27658,14 @@
       <c r="M1" s="137"/>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="270" t="s">
+      <c r="A2" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="270"/>
-      <c r="C2" s="270" t="s">
+      <c r="B2" s="267"/>
+      <c r="C2" s="267" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="267" t="s">
         <v>123</v>
       </c>
       <c r="E2" s="209" cm="1">
@@ -27658,12 +27696,12 @@
       <c r="M2" s="91"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="270" t="s">
+      <c r="A3" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="270"/>
-      <c r="C3" s="270"/>
-      <c r="D3" s="270"/>
+      <c r="B3" s="267"/>
+      <c r="C3" s="267"/>
+      <c r="D3" s="267"/>
       <c r="E3" s="209" cm="1">
         <f t="array" ref="E3">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A3:A3)</f>
         <v>0</v>
@@ -27692,14 +27730,14 @@
       <c r="M3" s="91"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="270" t="s">
+      <c r="A4" s="267" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="270"/>
-      <c r="C4" s="270" t="s">
+      <c r="B4" s="267"/>
+      <c r="C4" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="270"/>
+      <c r="D4" s="267"/>
       <c r="E4" s="209" cm="1">
         <f t="array" ref="E4">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A4:A4)</f>
         <v>0</v>
@@ -27728,12 +27766,12 @@
       <c r="M4" s="91"/>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="270" t="s">
+      <c r="A5" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="270"/>
-      <c r="C5" s="270"/>
-      <c r="D5" s="270"/>
+      <c r="B5" s="267"/>
+      <c r="C5" s="267"/>
+      <c r="D5" s="267"/>
       <c r="E5" s="209" cm="1">
         <f t="array" ref="E5">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A5:A5)</f>
         <v>0</v>
@@ -27762,12 +27800,12 @@
       <c r="M5" s="91"/>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="270" t="s">
+      <c r="A6" s="267" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="270"/>
-      <c r="C6" s="270"/>
-      <c r="D6" s="270"/>
+      <c r="B6" s="267"/>
+      <c r="C6" s="267"/>
+      <c r="D6" s="267"/>
       <c r="E6" s="209" cm="1">
         <f t="array" ref="E6">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A6:A6)</f>
         <v>0</v>
@@ -27796,14 +27834,14 @@
       <c r="M6" s="91"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="270" t="s">
+      <c r="A7" s="267" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="270"/>
+      <c r="B7" s="267"/>
       <c r="C7" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="270"/>
+      <c r="D7" s="267"/>
       <c r="E7" s="209" cm="1">
         <f t="array" ref="E7">+SUMIFS('Recursos aprobados'!G:G,'Recursos aprobados'!A:A,'FORM RESUMEN '!$D$5,'Recursos aprobados'!F:F,"AOMC",'Recursos aprobados'!E:E,'FORM 1 GASTO AO&amp;M-C SPEE'!A7:A7)</f>
         <v>0</v>
@@ -27832,10 +27870,10 @@
       <c r="M7" s="91"/>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="270" t="s">
+      <c r="A8" s="267" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="270"/>
+      <c r="B8" s="267"/>
       <c r="C8" s="132" t="s">
         <v>6</v>
       </c>
@@ -27870,10 +27908,10 @@
       <c r="M8" s="91"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="270" t="s">
+      <c r="A9" s="267" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="270"/>
+      <c r="B9" s="267"/>
       <c r="C9" s="132" t="s">
         <v>129</v>
       </c>
@@ -27908,12 +27946,12 @@
       <c r="M9" s="91"/>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="271" t="s">
+      <c r="A10" s="266" t="s">
         <v>294</v>
       </c>
-      <c r="B10" s="271"/>
-      <c r="C10" s="271"/>
-      <c r="D10" s="271"/>
+      <c r="B10" s="266"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="266"/>
       <c r="E10" s="208">
         <f>SUM(E2:E9)</f>
         <v>0</v>
@@ -27964,10 +28002,10 @@
       <c r="M11" s="91"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="266" t="s">
+      <c r="A12" s="268" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="267"/>
+      <c r="B12" s="269"/>
       <c r="C12" s="229">
         <v>0</v>
       </c>
@@ -27987,10 +28025,10 @@
       <c r="M12" s="141"/>
     </row>
     <row r="13" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="268" t="s">
+      <c r="A13" s="270" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="269"/>
+      <c r="B13" s="271"/>
       <c r="C13" s="230">
         <f>+C12+K10</f>
         <v>0</v>
@@ -28039,6 +28077,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D7"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A10:D10"/>
@@ -28047,14 +28093,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="El dato ingresado debe ser numérico y mayor y positivo." sqref="F2:F9 H2:L9 C12" xr:uid="{00000000-0002-0000-0800-000000000000}">
@@ -33683,7 +33721,10 @@
       <c r="L2" s="149"/>
       <c r="M2" s="149"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="152"/>
+      <c r="O2" s="152" t="str">
+        <f>+IF($M2="No iniciado 0%",0%,IF($M2="Elaboración de pliegos 5%",5%,IF($M2="Disponibilidad de pliegos 10%",10%,IF($M2="Publicación del proceso 15%",15%,IF($M2="Resolución de adjudicación 30%",30%,IF($M2="Adjudicación y firma de contrato 40%",40%,IF($M2="En ejecución 41% - 90%",(40%+($N2*50%)),IF($M2="Acta de entrega - recepción 95%",IF($N2=100%,95%,""),IF($M2="Registro contable 100%",IF($N2=100%,100%,""),"")))))))))</f>
+        <v/>
+      </c>
       <c r="P2" s="173"/>
       <c r="Q2" s="173"/>
       <c r="R2" s="149"/>
@@ -33691,7 +33732,7 @@
       <c r="T2" s="238"/>
       <c r="U2" s="238"/>
       <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
+      <c r="W2" s="287"/>
       <c r="X2" s="238"/>
       <c r="Y2" s="238"/>
       <c r="Z2" s="238"/>
@@ -33736,7 +33777,7 @@
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="N2:O2 S2:BE2" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Solo se permiten datos numericos" sqref="N2:O2 S2:V2 X2:BE2" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>ISNUMBER(N2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 J2" xr:uid="{00000000-0002-0000-0B00-000001000000}">
